--- a/config-import/baccara-config-2026-10-04.xlsx
+++ b/config-import/baccara-config-2026-10-04.xlsx
@@ -486,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -543,16 +543,49 @@
         <v>non</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>-1003991686866</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Bot 2</v>
+      </c>
+      <c r="C6" t="str">
+        <v>non</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>-1003932129001</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Bot 1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>non</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>-1004368493318</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Bot3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>non</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AP14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -637,42 +670,48 @@
         <v>channels</v>
       </c>
       <c r="AB1" t="str">
+        <v>delayEnabled</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>delaySec</v>
+      </c>
+      <c r="AD1" t="str">
         <v>formatDistribution</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>startGame</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>varStep</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>decalage</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>streak</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>absence</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>scope</v>
       </c>
-      <c r="AI1" t="str">
+      <c r="AK1" t="str">
         <v>channelInfos</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AL1" t="str">
         <v>token</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AM1" t="str">
         <v>gap</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AN1" t="str">
         <v>sentCount</v>
       </c>
-      <c r="AM1" t="str">
+      <c r="AO1" t="str">
         <v>lastSentAt</v>
       </c>
-      <c r="AN1" t="str">
+      <c r="AP1" t="str">
         <v>entries</v>
       </c>
     </row>
@@ -758,35 +797,35 @@
       <c r="AA2" t="str">
         <v>[]</v>
       </c>
-      <c r="AB2">
-        <v>1</v>
+      <c r="AB2" t="b">
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2">
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>4</v>
-      </c>
-      <c r="AH2" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>3</v>
+      </c>
+      <c r="AI2">
+        <v>4</v>
+      </c>
+      <c r="AJ2" t="str">
         <v>tous</v>
       </c>
-      <c r="AI2" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ2" t="str">
-        <v/>
-      </c>
       <c r="AK2" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL2" t="str">
         <v/>
@@ -795,6 +834,12 @@
         <v/>
       </c>
       <c r="AN2" t="str">
+        <v/>
+      </c>
+      <c r="AO2" t="str">
+        <v/>
+      </c>
+      <c r="AP2" t="str">
         <v/>
       </c>
     </row>
@@ -880,43 +925,49 @@
       <c r="AA3" t="str">
         <v>[]</v>
       </c>
-      <c r="AB3">
-        <v>1</v>
+      <c r="AB3" t="b">
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3">
         <v>1</v>
       </c>
       <c r="AF3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>4</v>
-      </c>
-      <c r="AH3" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <v>3</v>
+      </c>
+      <c r="AI3">
+        <v>4</v>
+      </c>
+      <c r="AJ3" t="str">
         <v>tous</v>
       </c>
-      <c r="AI3" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ3" t="str">
-        <v/>
-      </c>
-      <c r="AK3">
-        <v>3</v>
+      <c r="AK3" t="str">
+        <v>[]</v>
       </c>
       <c r="AL3" t="str">
         <v/>
       </c>
-      <c r="AM3" t="str">
-        <v/>
+      <c r="AM3">
+        <v>3</v>
       </c>
       <c r="AN3" t="str">
+        <v/>
+      </c>
+      <c r="AO3" t="str">
+        <v/>
+      </c>
+      <c r="AP3" t="str">
         <v/>
       </c>
     </row>
@@ -1002,35 +1053,35 @@
       <c r="AA4" t="str">
         <v>[]</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>10</v>
+      </c>
+      <c r="AD4">
         <v>79</v>
       </c>
-      <c r="AC4">
-        <v>1</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
       <c r="AE4">
         <v>1</v>
       </c>
       <c r="AF4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>4</v>
-      </c>
-      <c r="AH4" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>3</v>
+      </c>
+      <c r="AI4">
+        <v>4</v>
+      </c>
+      <c r="AJ4" t="str">
         <v>tous</v>
       </c>
-      <c r="AI4" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ4" t="str">
-        <v/>
-      </c>
       <c r="AK4" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL4" t="str">
         <v/>
@@ -1039,6 +1090,12 @@
         <v/>
       </c>
       <c r="AN4" t="str">
+        <v/>
+      </c>
+      <c r="AO4" t="str">
+        <v/>
+      </c>
+      <c r="AP4" t="str">
         <v/>
       </c>
     </row>
@@ -1124,43 +1181,49 @@
       <c r="AA5" t="str">
         <v>[-1003209054618]</v>
       </c>
-      <c r="AB5">
-        <v>1</v>
+      <c r="AB5" t="b">
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5">
         <v>1</v>
       </c>
       <c r="AF5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>4</v>
-      </c>
-      <c r="AH5" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>3</v>
+      </c>
+      <c r="AI5">
+        <v>4</v>
+      </c>
+      <c r="AJ5" t="str">
         <v>tous</v>
       </c>
-      <c r="AI5" t="str">
+      <c r="AK5" t="str">
         <v>[{"id":-1003209054618,"type":"channel","error":null,"title":"Parité pair impair","canPost":true,"username":null,"confirmed":true,"memberCount":4}]</v>
       </c>
-      <c r="AJ5" t="str">
-        <v/>
-      </c>
-      <c r="AK5" t="str">
-        <v/>
-      </c>
-      <c r="AL5">
-        <v>522</v>
-      </c>
-      <c r="AM5">
-        <v>1791152980394</v>
-      </c>
-      <c r="AN5" t="str">
+      <c r="AL5" t="str">
+        <v/>
+      </c>
+      <c r="AM5" t="str">
+        <v/>
+      </c>
+      <c r="AN5">
+        <v>62</v>
+      </c>
+      <c r="AO5">
+        <v>1791192607193</v>
+      </c>
+      <c r="AP5" t="str">
         <v/>
       </c>
     </row>
@@ -1246,35 +1309,35 @@
       <c r="AA6" t="str">
         <v>[]</v>
       </c>
-      <c r="AB6">
-        <v>1</v>
+      <c r="AB6" t="b">
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6">
         <v>1</v>
       </c>
       <c r="AF6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>4</v>
-      </c>
-      <c r="AH6" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>3</v>
+      </c>
+      <c r="AI6">
+        <v>4</v>
+      </c>
+      <c r="AJ6" t="str">
         <v>tous</v>
       </c>
-      <c r="AI6" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ6" t="str">
-        <v/>
-      </c>
       <c r="AK6" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL6" t="str">
         <v/>
@@ -1283,6 +1346,12 @@
         <v/>
       </c>
       <c r="AN6" t="str">
+        <v/>
+      </c>
+      <c r="AO6" t="str">
+        <v/>
+      </c>
+      <c r="AP6" t="str">
         <v/>
       </c>
     </row>
@@ -1368,35 +1437,35 @@
       <c r="AA7" t="str">
         <v>[]</v>
       </c>
-      <c r="AB7">
-        <v>1</v>
+      <c r="AB7" t="b">
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <v>1</v>
       </c>
       <c r="AF7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>3</v>
-      </c>
-      <c r="AH7" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>3</v>
+      </c>
+      <c r="AI7">
+        <v>3</v>
+      </c>
+      <c r="AJ7" t="str">
         <v>tous</v>
       </c>
-      <c r="AI7" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ7" t="str">
-        <v/>
-      </c>
       <c r="AK7" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL7" t="str">
         <v/>
@@ -1405,6 +1474,12 @@
         <v/>
       </c>
       <c r="AN7" t="str">
+        <v/>
+      </c>
+      <c r="AO7" t="str">
+        <v/>
+      </c>
+      <c r="AP7" t="str">
         <v/>
       </c>
     </row>
@@ -1490,35 +1565,35 @@
       <c r="AA8" t="str">
         <v>[]</v>
       </c>
-      <c r="AB8">
-        <v>1</v>
+      <c r="AB8" t="b">
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8">
         <v>1</v>
       </c>
       <c r="AF8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>4</v>
-      </c>
-      <c r="AH8" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>3</v>
+      </c>
+      <c r="AI8">
+        <v>4</v>
+      </c>
+      <c r="AJ8" t="str">
         <v>tous</v>
       </c>
-      <c r="AI8" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ8" t="str">
-        <v/>
-      </c>
       <c r="AK8" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL8" t="str">
         <v/>
@@ -1527,6 +1602,12 @@
         <v/>
       </c>
       <c r="AN8" t="str">
+        <v/>
+      </c>
+      <c r="AO8" t="str">
+        <v/>
+      </c>
+      <c r="AP8" t="str">
         <v/>
       </c>
     </row>
@@ -1612,35 +1693,35 @@
       <c r="AA9" t="str">
         <v>[]</v>
       </c>
-      <c r="AB9">
-        <v>1</v>
+      <c r="AB9" t="b">
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9">
         <v>1</v>
       </c>
       <c r="AF9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>4</v>
-      </c>
-      <c r="AH9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>3</v>
+      </c>
+      <c r="AI9">
+        <v>4</v>
+      </c>
+      <c r="AJ9" t="str">
         <v>tous</v>
       </c>
-      <c r="AI9" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ9" t="str">
-        <v/>
-      </c>
       <c r="AK9" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL9" t="str">
         <v/>
@@ -1649,6 +1730,12 @@
         <v/>
       </c>
       <c r="AN9" t="str">
+        <v/>
+      </c>
+      <c r="AO9" t="str">
+        <v/>
+      </c>
+      <c r="AP9" t="str">
         <v/>
       </c>
     </row>
@@ -1734,43 +1821,49 @@
       <c r="AA10" t="str">
         <v>[-1004462324745]</v>
       </c>
-      <c r="AB10">
-        <v>1</v>
+      <c r="AB10" t="b">
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10">
         <v>1</v>
       </c>
       <c r="AF10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>4</v>
-      </c>
-      <c r="AH10" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>3</v>
+      </c>
+      <c r="AI10">
+        <v>4</v>
+      </c>
+      <c r="AJ10" t="str">
         <v>tous</v>
       </c>
-      <c r="AI10" t="str">
+      <c r="AK10" t="str">
         <v>[{"id":-1004462324745,"type":"channel","error":null,"title":"BACCARA FREE BOT","canPost":true,"username":null,"confirmed":true,"memberCount":5}]</v>
       </c>
-      <c r="AJ10" t="str">
-        <v/>
-      </c>
-      <c r="AK10" t="str">
-        <v/>
-      </c>
-      <c r="AL10">
-        <v>493</v>
-      </c>
-      <c r="AM10">
-        <v>1791153010417</v>
-      </c>
-      <c r="AN10" t="str">
+      <c r="AL10" t="str">
+        <v/>
+      </c>
+      <c r="AM10" t="str">
+        <v/>
+      </c>
+      <c r="AN10">
+        <v>57</v>
+      </c>
+      <c r="AO10">
+        <v>1791192577204</v>
+      </c>
+      <c r="AP10" t="str">
         <v/>
       </c>
     </row>
@@ -1856,43 +1949,49 @@
       <c r="AA11" t="str">
         <v>[-1004483335797]</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" t="b">
         <v>1</v>
       </c>
       <c r="AC11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11">
         <v>1</v>
       </c>
       <c r="AF11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>4</v>
-      </c>
-      <c r="AH11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>3</v>
+      </c>
+      <c r="AI11">
+        <v>4</v>
+      </c>
+      <c r="AJ11" t="str">
         <v>tous</v>
       </c>
-      <c r="AI11" t="str">
+      <c r="AK11" t="str">
         <v>[{"id":-1004483335797,"title":"ELI et Kouamé","type":"channel","username":null,"memberCount":4,"canPost":true,"confirmed":true,"error":null}]</v>
       </c>
-      <c r="AJ11" t="str">
-        <v/>
-      </c>
-      <c r="AK11" t="str">
-        <v/>
-      </c>
-      <c r="AL11">
-        <v>959</v>
-      </c>
-      <c r="AM11">
-        <v>1791153070594</v>
-      </c>
-      <c r="AN11" t="str">
+      <c r="AL11" t="str">
+        <v/>
+      </c>
+      <c r="AM11" t="str">
+        <v/>
+      </c>
+      <c r="AN11">
+        <v>118</v>
+      </c>
+      <c r="AO11">
+        <v>1791192917456</v>
+      </c>
+      <c r="AP11" t="str">
         <v/>
       </c>
     </row>
@@ -1978,35 +2077,35 @@
       <c r="AA12" t="str">
         <v>[]</v>
       </c>
-      <c r="AB12">
-        <v>1</v>
+      <c r="AB12" t="b">
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12">
         <v>1</v>
       </c>
       <c r="AF12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>4</v>
-      </c>
-      <c r="AH12" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>3</v>
+      </c>
+      <c r="AI12">
+        <v>4</v>
+      </c>
+      <c r="AJ12" t="str">
         <v>tous</v>
       </c>
-      <c r="AI12" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ12" t="str">
-        <v/>
-      </c>
       <c r="AK12" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL12" t="str">
         <v/>
@@ -2015,6 +2114,12 @@
         <v/>
       </c>
       <c r="AN12" t="str">
+        <v/>
+      </c>
+      <c r="AO12" t="str">
+        <v/>
+      </c>
+      <c r="AP12" t="str">
         <v/>
       </c>
     </row>
@@ -2100,35 +2205,35 @@
       <c r="AA13" t="str">
         <v>[]</v>
       </c>
-      <c r="AB13">
-        <v>1</v>
+      <c r="AB13" t="b">
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13">
         <v>1</v>
       </c>
       <c r="AF13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>4</v>
-      </c>
-      <c r="AH13" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <v>3</v>
+      </c>
+      <c r="AI13">
+        <v>4</v>
+      </c>
+      <c r="AJ13" t="str">
         <v>tous</v>
       </c>
-      <c r="AI13" t="str">
-        <v>[]</v>
-      </c>
-      <c r="AJ13" t="str">
-        <v/>
-      </c>
       <c r="AK13" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL13" t="str">
         <v/>
@@ -2137,6 +2242,12 @@
         <v/>
       </c>
       <c r="AN13" t="str">
+        <v/>
+      </c>
+      <c r="AO13" t="str">
+        <v/>
+      </c>
+      <c r="AP13" t="str">
         <v>[]</v>
       </c>
     </row>
@@ -2213,8 +2324,8 @@
       <c r="X14">
         <v>0</v>
       </c>
-      <c r="Y14" t="str">
-        <v/>
+      <c r="Y14">
+        <v>1</v>
       </c>
       <c r="Z14" t="str">
         <v/>
@@ -2222,35 +2333,35 @@
       <c r="AA14" t="str">
         <v>[]</v>
       </c>
-      <c r="AB14" t="str">
-        <v/>
-      </c>
-      <c r="AC14" t="str">
-        <v/>
-      </c>
-      <c r="AD14" t="str">
-        <v/>
+      <c r="AB14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>10</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
       </c>
       <c r="AE14">
-        <v>2</v>
-      </c>
-      <c r="AF14" t="str">
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>4</v>
-      </c>
-      <c r="AH14" t="str">
-        <v/>
-      </c>
-      <c r="AI14" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="AH14">
+        <v>3</v>
+      </c>
+      <c r="AI14">
+        <v>4</v>
       </c>
       <c r="AJ14" t="str">
-        <v/>
+        <v>tous</v>
       </c>
       <c r="AK14" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="AL14" t="str">
         <v/>
@@ -2259,12 +2370,18 @@
         <v/>
       </c>
       <c r="AN14" t="str">
+        <v/>
+      </c>
+      <c r="AO14" t="str">
+        <v/>
+      </c>
+      <c r="AP14" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AP14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2356,7 +2473,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2388,40 +2505,40 @@
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"format":89,"maxR":3,"lossNoticeEnabled":false},"trackers":[{"id":"t-1790535182855-8d5br","key":"dizaine","name":"88","category":1,"triggers":{"r1":{"enabled":false,"n":0},"r2":{"enabled":false,"n":0},"r3":{"enabled":false,"n":0},"perdue":{"enabled":false,"n":0}},"repeat":{"enabled":false,"lead":5,"mode":"meme"},"streak":{"enabled":false,"count":3,"n":4,"nj":4},"decade":{"enabled":true,"count":3,"n":8,"ni":10,"nk":4},"lastDecadeEnd":1224,"decadeSession":null,"lastStreakEnd":0,"streakProgress":null,"streakSession":null,"channels":[-1003985232619],"siteChannelId":null,"format":88,"maxR":3,"lastRepeatSource":0,"counting":false,"armedTrigger":null,"armedNeeded":0,"armedSeen":0,"armedTrail":[],"armed":false,"armedAt":null,"sentCount":233,"lastSentAt":1791147194758,"createdAt":1790535182855},{"id":"t-1790535342432-63oin","key":"ombreJoueur","name":"89","category":3,"triggers":{"r1":{"enabled":false,"n":0},"r2":{"enabled":false,"n":0},"r3":{"enabled":false,"n":0},"perdue":{"enabled":false,"n":0}},"repeat":{"enabled":false,"lead":5,"mode":"meme"},"streak":{"enabled":true,"count":3,"n":3,"nj":3},"decade":{"enabled":false,"count":3,"n":8,"ni":10,"nk":4},"lastDecadeEnd":0,"decadeSession":null,"lastStreakEnd":754,"streakProgress":{"suit":"♣️","seen":1,"count":3,"updatedAt":1791153105392},"streakSession":null,"channels":[-1003985232619],"siteChannelId":null,"format":89,"maxR":3,"lastRepeatSource":0,"counting":false,"armedTrigger":null,"armedNeeded":0,"armedSeen":0,"armedTrail":[],"armed":false,"armedAt":null,"sentCount":82,"lastSentAt":1791116983136,"createdAt":1790535342432}],"history":[{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":1262,"suit":"❤️","sentAt":1791147194758,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 4/4 à +10 (#N1262)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":1252,"suit":"❤️","sentAt":1791146474775,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 3/4 à +10 (#N1252)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":1242,"suit":"❤️","sentAt":1791145874641,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 2/4 à +10 (#N1242)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":1232,"suit":"♦️","sentAt":1791145334519,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N1232)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":1222,"suit":"♦️","sentAt":1791144759540,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N1222)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":1212,"suit":"♦️","sentAt":1791144189484,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N1212)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":1202,"suit":"♦️","sentAt":1791143405283,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":1092,"suit":"♦️","sentAt":1791136898436,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N1092)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":1082,"suit":"♦️","sentAt":1791136328284,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N1082)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":1072,"suit":"♦️","sentAt":1791135698484,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N1072)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":1062,"suit":"♦️","sentAt":1791134953844,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":1052,"suit":"♦️","sentAt":1791134683132,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N1052)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":1042,"suit":"♦️","sentAt":1791133963042,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N1042)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":1032,"suit":"♦️","sentAt":1791133297847,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N1032)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":1022,"suit":"♦️","sentAt":1791132548294,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":992,"suit":"♦️","sentAt":1791130877438,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N992)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":982,"suit":"♦️","sentAt":1791130277635,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N982)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":972,"suit":"♦️","sentAt":1791129877361,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N972)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":962,"suit":"♦️","sentAt":1791128952430,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":902,"suit":"❤️","sentAt":1791125526998,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 4/4 à +10 (#N902)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":892,"suit":"❤️","sentAt":1791125022413,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 3/4 à +10 (#N892)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":882,"suit":"❤️","sentAt":1791124336914,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 2/4 à +10 (#N882)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":872,"suit":"❤️","sentAt":1791123577896,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":763,"suit":"♣️","sentAt":1791116983136,"category":3,"trail":[{"target":736,"suit":"♣️","status":"gagné"},{"target":749,"suit":"♣️","status":"gagné"},{"target":754,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N754) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":760,"suit":"♣️","sentAt":1791116982900,"category":3,"trail":[{"target":736,"suit":"♣️","status":"gagné"},{"target":749,"suit":"♣️","status":"gagné"},{"target":754,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N754) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":757,"suit":"♣️","sentAt":1791116982615,"category":3,"trail":[{"target":736,"suit":"♣️","status":"gagné"},{"target":749,"suit":"♣️","status":"gagné"},{"target":754,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N754) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":452,"suit":"♦️","sentAt":1791098583883,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N452)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":442,"suit":"♦️","sentAt":1791097904303,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N442)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":432,"suit":"♦️","sentAt":1791097394292,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N432)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":422,"suit":"♦️","sentAt":1791096578707,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":412,"suit":"♦️","sentAt":1791096314083,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N412)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":402,"suit":"♦️","sentAt":1791095653930,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N402)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":392,"suit":"♦️","sentAt":1791095113819,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N392)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":382,"suit":"♦️","sentAt":1791094208309,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":282,"suit":"♦️","sentAt":1791088452803,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N282)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":272,"suit":"♦️","sentAt":1791087912701,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N272)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":262,"suit":"♦️","sentAt":1791087072605,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N262)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":252,"suit":"♦️","sentAt":1791086348648,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":212,"suit":"♦️","sentAt":1791084312493,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N212)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":202,"suit":"♦️","sentAt":1791083532288,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N202)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":192,"suit":"♦️","sentAt":1791082967428,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N192)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":182,"suit":"♦️","sentAt":1791082172515,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":1113,"suit":"♦️","sentAt":1791051548981,"category":3,"trail":[{"target":1083,"suit":"♦️","status":"gagné"},{"target":1088,"suit":"♦️","status":"gagné"},{"target":1104,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N1104) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":1110,"suit":"♦️","sentAt":1791051548763,"category":3,"trail":[{"target":1083,"suit":"♦️","status":"gagné"},{"target":1088,"suit":"♦️","status":"gagné"},{"target":1104,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N1104) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":1107,"suit":"♦️","sentAt":1791051548543,"category":3,"trail":[{"target":1083,"suit":"♦️","status":"gagné"},{"target":1088,"suit":"♦️","status":"gagné"},{"target":1104,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N1104) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":1102,"suit":"❤️","sentAt":1791051133238,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 4/4 à +10 (#N1102)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":1092,"suit":"❤️","sentAt":1791050503134,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 3/4 à +10 (#N1092)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":1082,"suit":"❤️","sentAt":1791050058018,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 2/4 à +10 (#N1082)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":1072,"suit":"❤️","sentAt":1791049153280,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":1012,"suit":"❤️","sentAt":1791045847412,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 4/4 à +10 (#N1012)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":1002,"suit":"❤️","sentAt":1791045127209,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 3/4 à +10 (#N1002)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":992,"suit":"❤️","sentAt":1791044597308,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 2/4 à +10 (#N992)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":982,"suit":"❤️","sentAt":1791043782730,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":748,"suit":"♣️","sentAt":1791029651736,"category":3,"trail":[{"target":723,"suit":"♣️","status":"gagné"},{"target":734,"suit":"♣️","status":"gagné"},{"target":739,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N739) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":745,"suit":"♣️","sentAt":1791029651484,"category":3,"trail":[{"target":723,"suit":"♣️","status":"gagné"},{"target":734,"suit":"♣️","status":"gagné"},{"target":739,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N739) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":742,"suit":"♣️","sentAt":1791029651184,"category":3,"trail":[{"target":723,"suit":"♣️","status":"gagné"},{"target":734,"suit":"♣️","status":"gagné"},{"target":739,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N739) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":612,"suit":"♦️","sentAt":1791021729817,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N612)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":602,"suit":"♦️","sentAt":1791021069525,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N602)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":592,"suit":"♦️","sentAt":1791020594502,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N592)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":582,"suit":"♦️","sentAt":1791019749880,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":457,"suit":"♦️","sentAt":1791012215224,"category":3,"trail":[{"target":423,"suit":"♦️","status":"perdu"},{"target":434,"suit":"♦️","status":"gagné"},{"target":448,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N448) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":454,"suit":"♦️","sentAt":1791012214932,"category":3,"trail":[{"target":423,"suit":"♦️","status":"perdu"},{"target":434,"suit":"♦️","status":"gagné"},{"target":448,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N448) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":451,"suit":"♦️","sentAt":1791012214693,"category":3,"trail":[{"target":423,"suit":"♦️","status":"perdu"},{"target":434,"suit":"♦️","status":"gagné"},{"target":448,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N448) → prédit 1/3 à +3"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":244,"suit":"♣️","sentAt":1790999432252,"category":3,"trail":[{"target":220,"suit":"♣️","status":"gagné"},{"target":225,"suit":"♣️","status":"gagné"},{"target":235,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N235) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":241,"suit":"♣️","sentAt":1790999432038,"category":3,"trail":[{"target":220,"suit":"♣️","status":"gagné"},{"target":225,"suit":"♣️","status":"gagné"},{"target":235,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N235) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":238,"suit":"♣️","sentAt":1790999431822,"category":3,"trail":[{"target":220,"suit":"♣️","status":"gagné"},{"target":225,"suit":"♣️","status":"gagné"},{"target":235,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N235) → prédit 1/3 à +3"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":193,"suit":"♠️","sentAt":1790996402810,"category":3,"trail":[{"target":155,"suit":"♠️","status":"gagné"},{"target":166,"suit":"♠️","status":"gagné"},{"target":184,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N184) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":190,"suit":"♠️","sentAt":1790996402588,"category":3,"trail":[{"target":155,"suit":"♠️","status":"gagné"},{"target":166,"suit":"♠️","status":"gagné"},{"target":184,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N184) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":187,"suit":"♠️","sentAt":1790996402346,"category":3,"trail":[{"target":155,"suit":"♠️","status":"gagné"},{"target":166,"suit":"♠️","status":"gagné"},{"target":184,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N184) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":102,"suit":"♦️","sentAt":1790991106908,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N102)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":92,"suit":"♦️","sentAt":1790990536796,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N92)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":82,"suit":"♦️","sentAt":1790989876669,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N82)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":72,"suit":"♦️","sentAt":1790989201367,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":1396,"suit":"♣️","sentAt":1790982131354,"category":3,"trail":[{"target":1355,"suit":"♣️","status":"perdu"},{"target":1367,"suit":"♣️","status":"perdu"},{"target":1387,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N1387) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":1393,"suit":"♣️","sentAt":1790982131140,"category":3,"trail":[{"target":1355,"suit":"♣️","status":"perdu"},{"target":1367,"suit":"♣️","status":"perdu"},{"target":1387,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N1387) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":1390,"suit":"♣️","sentAt":1790982130914,"category":3,"trail":[{"target":1355,"suit":"♣️","status":"perdu"},{"target":1367,"suit":"♣️","status":"perdu"},{"target":1387,"suit":"♣️","status":"en attente"}],"note":"Série 3/3 de ♣️ (fin #N1387) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":1382,"suit":"♦️","sentAt":1790981565983,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N1382)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":1372,"suit":"♦️","sentAt":1790980935606,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N1372)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":1362,"suit":"♦️","sentAt":1790980335587,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N1362)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":1352,"suit":"♦️","sentAt":1790979575518,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":1351,"suit":"♦️","sentAt":1790979461206,"category":3,"trail":[{"target":1314,"suit":"♦️","status":"gagné"},{"target":1332,"suit":"♦️","status":"gagné"},{"target":1342,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N1342) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":1348,"suit":"♦️","sentAt":1790979460965,"category":3,"trail":[{"target":1314,"suit":"♦️","status":"gagné"},{"target":1332,"suit":"♦️","status":"gagné"},{"target":1342,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N1342) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":1345,"suit":"♦️","sentAt":1790979460740,"category":3,"trail":[{"target":1314,"suit":"♦️","status":"gagné"},{"target":1332,"suit":"♦️","status":"gagné"},{"target":1342,"suit":"♦️","status":"en attente"}],"note":"Série 3/3 de ♦️ (fin #N1342) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":952,"suit":"♠️","sentAt":1790955732182,"category":1,"trail":[],"note":"Comptage dizaine ♠️ → prédit 4/4 à +10 (#N952)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":942,"suit":"♠️","sentAt":1790955096926,"category":1,"trail":[],"note":"Comptage dizaine ♠️ → prédit 3/4 à +10 (#N942)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":932,"suit":"♠️","sentAt":1790954526976,"category":1,"trail":[],"note":"Comptage dizaine ♠️ → prédit 2/4 à +10 (#N932)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":922,"suit":"♠️","sentAt":1790953782222,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":838,"suit":"♠️","sentAt":1790948702545,"category":3,"trail":[{"target":799,"suit":"♠️","status":"gagné"},{"target":805,"suit":"♠️","status":"gagné"},{"target":829,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N829) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":835,"suit":"♠️","sentAt":1790948702293,"category":3,"trail":[{"target":799,"suit":"♠️","status":"gagné"},{"target":805,"suit":"♠️","status":"gagné"},{"target":829,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N829) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":832,"suit":"♠️","sentAt":1790948702038,"category":3,"trail":[{"target":799,"suit":"♠️","status":"gagné"},{"target":805,"suit":"♠️","status":"gagné"},{"target":829,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N829) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":812,"suit":"❤️","sentAt":1790947366570,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 4/4 à +10 (#N812)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":802,"suit":"❤️","sentAt":1790946726308,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 3/4 à +10 (#N802)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":792,"suit":"❤️","sentAt":1790946186216,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 2/4 à +10 (#N792)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":782,"suit":"❤️","sentAt":1790945496116,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 4/4 à +10 (#N782)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":772,"suit":"❤️","sentAt":1790945086035,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 3/4 à +10 (#N772)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":762,"suit":"❤️","sentAt":1790944325946,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 2/4 à +10 (#N762)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":752,"suit":"❤️","sentAt":1790943581388,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":592,"suit":"♣️","sentAt":1790934184423,"category":1,"trail":[],"note":"Comptage dizaine ♣️ → prédit 4/4 à +10 (#N592)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":582,"suit":"♣️","sentAt":1790933684423,"category":1,"trail":[],"note":"Comptage dizaine ♣️ → prédit 3/4 à +10 (#N582)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":572,"suit":"♣️","sentAt":1790932924813,"category":1,"trail":[],"note":"Comptage dizaine ♣️ → prédit 2/4 à +10 (#N572)"}],"tally":{"t-1789459347620-155he":{"win":0,"loss":0,"cancelled":0,"total":0,"lastAt":null},"t-1790535182855-8d5br":{"win":197,"loss":34,"cancelled":0,"total":231,"lastAt":1791147669993},"t-1790535342432-63oin":{"win":77,"loss":5,"cancelled":0,"total":82,"lastAt":1791117842098}},"verified":{"t-1790535342432-63oin":[{"target":457,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791013084091},{"target":742,"suit":"♣️","status":"gagné","step":2,"maxR":3,"at":1791030190788},{"target":745,"suit":"♣️","status":"gagné","step":0,"maxR":3,"at":1791030281298},{"target":748,"suit":"♣️","status":"gagné","step":1,"maxR":3,"at":1791030541396},{"target":1107,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791051968494},{"target":1110,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791052268185},{"target":1113,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791052418383},{"target":757,"suit":"♣️","status":"gagné","step":2,"maxR":3,"at":1791117541388},{"target":760,"suit":"♣️","status":"perdu","step":3,"maxR":3,"at":1791117726696},{"target":763,"suit":"♣️","status":"gagné","step":1,"maxR":3,"at":1791117842098}],"t-1790535182855-8d5br":[{"target":1072,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791136322994},{"target":1082,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791136893099},{"target":1092,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791137553185},{"target":1202,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791144184196},{"target":1212,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791144754190},{"target":1222,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791145329290},{"target":1232,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791145870088},{"target":1242,"suit":"❤️","status":"gagné","step":0,"maxR":3,"at":1791146469687},{"target":1252,"suit":"❤️","status":"gagné","step":1,"maxR":3,"at":1791147190095},{"target":1262,"suit":"❤️","status":"gagné","step":0,"maxR":3,"at":1791147669993}]},"sentKeys":[{"key":"182|♦️","target":182,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791082171891},{"key":"192|♦️","target":192,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791082967085},{"key":"202|♦️","target":202,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791083531992},{"key":"212|♦️","target":212,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791084312185},{"key":"252|♦️","target":252,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791086347395},{"key":"262|♦️","target":262,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791087072293},{"key":"272|♦️","target":272,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791087912396},{"key":"282|♦️","target":282,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791088452583},{"key":"382|♦️","target":382,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791094208084},{"key":"392|♦️","target":392,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791095113584},{"key":"402|♦️","target":402,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791095653590},{"key":"412|♦️","target":412,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791096313690},{"key":"422|♦️","target":422,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791096578394},{"key":"432|♦️","target":432,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791097393895},{"key":"442|♦️","target":442,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791097903990},{"key":"452|♦️","target":452,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791098583493},{"key":"757|♣️","target":757,"suit":"♣️","trackerId":"t-1790535342432-63oin","at":1791116981993},{"key":"760|♣️","target":760,"suit":"♣️","trackerId":"t-1790535342432-63oin","at":1791116982615},{"key":"763|♣️","target":763,"suit":"♣️","trackerId":"t-1790535342432-63oin","at":1791116982900},{"key":"872|❤️","target":872,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791123577285},{"key":"882|❤️","target":882,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791124336584},{"key":"892|❤️","target":892,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791125022096},{"key":"902|❤️","target":902,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791125526687},{"key":"962|♦️","target":962,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791128952183},{"key":"972|♦️","target":972,"suit":"♦️","trackerId":"t-179</v>
+        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"format":89,"maxR":3,"lossNoticeEnabled":false},"trackers":[{"id":"t-1790535182855-8d5br","key":"dizaine","name":"88","category":1,"triggers":{"r1":{"enabled":false,"n":0},"r2":{"enabled":false,"n":0},"r3":{"enabled":false,"n":0},"perdue":{"enabled":false,"n":0}},"repeat":{"enabled":false,"lead":5,"mode":"meme"},"streak":{"enabled":false,"count":3,"n":4,"nj":4},"decade":{"enabled":true,"count":3,"n":8,"ni":10,"nk":4},"lastDecadeEnd":444,"decadeSession":null,"lastStreakEnd":0,"streakProgress":null,"streakSession":null,"channels":[-1003985232619],"siteChannelId":null,"format":88,"maxR":3,"lastRepeatSource":0,"counting":false,"armedTrigger":null,"armedNeeded":0,"armedSeen":0,"armedTrail":[],"armed":false,"armedAt":null,"sentCount":252,"lastSentAt":1791186677069,"createdAt":1790535182855},{"id":"t-1790535342432-63oin","key":"ombreJoueur","name":"89","category":3,"triggers":{"r1":{"enabled":false,"n":0},"r2":{"enabled":false,"n":0},"r3":{"enabled":false,"n":0},"perdue":{"enabled":false,"n":0}},"repeat":{"enabled":false,"lead":5,"mode":"meme"},"streak":{"enabled":true,"count":3,"n":3,"nj":3},"decade":{"enabled":false,"count":3,"n":8,"ni":10,"nk":4},"lastDecadeEnd":0,"decadeSession":null,"lastStreakEnd":342,"streakProgress":{"suit":"♦️","seen":1,"count":3,"updatedAt":1791193027153},"streakSession":null,"channels":[-1003985232619],"siteChannelId":null,"format":89,"maxR":3,"lastRepeatSource":0,"counting":false,"armedTrigger":null,"armedNeeded":0,"armedSeen":0,"armedTrail":[],"armed":false,"armedAt":null,"sentCount":85,"lastSentAt":1791178651815,"createdAt":1790535342432}],"history":[{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":482,"suit":"♣️","sentAt":1791186677069,"category":1,"trail":[],"note":"Comptage dizaine ♣️ → prédit 4/4 à +10 (#N482)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":472,"suit":"♣️","sentAt":1791186072152,"category":1,"trail":[],"note":"Comptage dizaine ♣️ → prédit 3/4 à +10 (#N472)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":462,"suit":"♣️","sentAt":1791185531989,"category":1,"trail":[],"note":"Comptage dizaine ♣️ → prédit 2/4 à +10 (#N462)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":452,"suit":"♣️","sentAt":1791184747686,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":422,"suit":"♦️","sentAt":1791183097173,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N422)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":412,"suit":"♦️","sentAt":1791182557207,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N412)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":402,"suit":"♦️","sentAt":1791181996581,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N402)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":392,"suit":"♦️","sentAt":1791181151767,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":352,"suit":"♦️","sentAt":1791178931499,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N352)"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 3/3)","target":351,"suit":"♠️","sentAt":1791178651815,"category":3,"trail":[{"target":324,"suit":"♠️","status":"gagné"},{"target":329,"suit":"♠️","status":"gagné"},{"target":342,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N342) → prédit 3/3 à +9"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 2/3)","target":348,"suit":"♠️","sentAt":1791178651603,"category":3,"trail":[{"target":324,"suit":"♠️","status":"gagné"},{"target":329,"suit":"♠️","status":"gagné"},{"target":342,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N342) → prédit 2/3 à +6"},{"trackerId":"t-1790535342432-63oin","trackerName":"89 (série 3× même costume 1/3)","target":345,"suit":"♠️","sentAt":1791178651321,"category":3,"trail":[{"target":324,"suit":"♠️","status":"gagné"},{"target":329,"suit":"♠️","status":"gagné"},{"target":342,"suit":"♠️","status":"en attente"}],"note":"Série 3/3 de ♠️ (fin #N342) → prédit 1/3 à +3"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":342,"suit":"♦️","sentAt":1791178271883,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N342)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":332,"suit":"♦️","sentAt":1791177732151,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N332)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":322,"suit":"♦️","sentAt":1791177071674,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 4/4 à +10 (#N322)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":312,"suit":"♦️","sentAt":1791176471695,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 3/4 à +10 (#N312)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":302,"suit":"♦️","sentAt":1791175871631,"category":1,"trail":[],"note":"Comptage dizaine ♦️ → prédit 2/4 à +10 (#N302)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":292,"suit":"♦️","sentAt":1791175207006,"category":1,"trail":[],"note":null},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 4/4)","target":132,"suit":"❤️","sentAt":1791165855277,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 4/4 à +10 (#N132)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 3/4)","target":122,"suit":"❤️","sentAt":1791165075251,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 3/4 à +10 (#N122)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 2/4)","target":112,"suit":"❤️","sentAt":1791164475182,"category":1,"trail":[],"note":"Comptage dizaine ❤️ → prédit 2/4 à +10 (#N112)"},{"trackerId":"t-1790535182855-8d5br","trackerName":"88 (comptage dizaine 1/4)","target":102,"suit":"❤️","sentAt":1791163806137,"category":1,"trail":[],"note":null}],"tally":{"t-1789459347620-155he":{"win":0,"loss":0,"cancelled":0,"total":0,"lastAt":null},"t-1790535182855-8d5br":{"win":216,"loss":34,"cancelled":0,"total":250,"lastAt":1791187327258},"t-1790535342432-63oin":{"win":80,"loss":5,"cancelled":0,"total":85,"lastAt":1791179406757}},"verified":{"t-1790535342432-63oin":[{"target":748,"suit":"♣️","status":"gagné","step":1,"maxR":3,"at":1791030541396},{"target":1107,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791051968494},{"target":1110,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791052268185},{"target":1113,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791052418383},{"target":757,"suit":"♣️","status":"gagné","step":2,"maxR":3,"at":1791117541388},{"target":760,"suit":"♣️","status":"perdu","step":3,"maxR":3,"at":1791117726696},{"target":763,"suit":"♣️","status":"gagné","step":1,"maxR":3,"at":1791117842098},{"target":345,"suit":"♠️","status":"gagné","step":2,"maxR":3,"at":1791179166865},{"target":348,"suit":"♠️","status":"gagné","step":1,"maxR":3,"at":1791179316664},{"target":351,"suit":"♠️","status":"gagné","step":0,"maxR":3,"at":1791179406757}],"t-1790535182855-8d5br":[{"target":342,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791178926857},{"target":352,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791179466753},{"target":392,"suit":"♦️","status":"gagné","step":2,"maxR":3,"at":1791181991762},{"target":402,"suit":"♦️","status":"gagné","step":1,"maxR":3,"at":1791182551964},{"target":412,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791183092154},{"target":422,"suit":"♦️","status":"gagné","step":0,"maxR":3,"at":1791183666963},{"target":452,"suit":"♣️","status":"gagné","step":1,"maxR":3,"at":1791185527065},{"target":462,"suit":"♣️","status":"gagné","step":0,"maxR":3,"at":1791186067291},{"target":472,"suit":"♣️","status":"gagné","step":0,"maxR":3,"at":1791186671659},{"target":482,"suit":"♣️","status":"gagné","step":1,"maxR":3,"at":1791187327259}]},"sentKeys":[{"key":"102|❤️","target":102,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791163805546},{"key":"112|❤️","target":112,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791164474955},{"key":"122|❤️","target":122,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791165074959},{"key":"132|❤️","target":132,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791165855051},{"key":"292|♦️","target":292,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791175206661},{"key":"302|♦️","target":302,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791175871351},{"key":"312|♦️","target":312,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791176471363},{"key":"322|♦️","target":322,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791177071450},{"key":"332|♦️","target":332,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791177731456},{"key":"342|♦️","target":342,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791178271464},{"key":"345|♠️","target":345,"suit":"♠️","trackerId":"t-1790535342432-63oin","at":1791178651051},{"key":"348|♠️","target":348,"suit":"♠️","trackerId":"t-1790535342432-63oin","at":1791178651322},{"key":"351|♠️","target":351,"suit":"♠️","trackerId":"t-1790535342432-63oin","at":1791178651603},{"key":"352|♦️","target":352,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791178931158},{"key":"392|♦️","target":392,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791181151466},{"key":"402|♦️","target":402,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791181996352},{"key":"412|♦️","target":412,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791182556862},{"key":"422|♦️","target":422,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791183096951},{"key":"452|♣️","target":452,"suit":"♣️","trackerId":"t-1790535182855-8d5br","at":1791184747354},{"key":"462|♣️","target":462,"suit":"♣️","trackerId":"t-1790535182855-8d5br","at":1791185531657},{"key":"472|♣️","target":472,"suit":"♣️","trackerId":"t-1790535182855-8d5br","at":1791186071737},{"key":"482|♣️","target":482,"suit":"♣️","trackerId":"t-1790535182855-8d5br","at":1791186676661}],"sentCount":337,"lastSentAt":1791186677069}</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>afterLoss</v>
+        <v>combined</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="str">
-        <v>0535182855-8d5br","at":1791129877083},{"key":"982|♦️","target":982,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791130277208},{"key":"992|♦️","target":992,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791130877186},{"key":"1022|♦️","target":1022,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791132547897},{"key":"1032|♦️","target":1032,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791133297493},{"key":"1042|♦️","target":1042,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791133962689},{"key":"1052|♦️","target":1052,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791134682787},{"key":"1062|♦️","target":1062,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791134953496},{"key":"1072|♦️","target":1072,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791135697884},{"key":"1082|♦️","target":1082,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791136327894},{"key":"1092|♦️","target":1092,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791136898083},{"key":"1202|♦️","target":1202,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791143404491},{"key":"1212|♦️","target":1212,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791144188996},{"key":"1222|♦️","target":1222,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791144759191},{"key":"1232|♦️","target":1232,"suit":"♦️","trackerId":"t-1790535182855-8d5br","at":1791145334192},{"key":"1242|❤️","target":1242,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791145874287},{"key":"1252|❤️","target":1252,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791146474390},{"key":"1262|❤️","target":1262,"suit":"❤️","trackerId":"t-1790535182855-8d5br","at":1791147194397}],"sentCount":315,"lastSentAt":1791147194758}</v>
+        <v>{"config":{"enabled":true,"channels":[],"format":1,"maxR":1},"trackers":[{"id":"ct-1","key":"dominant","name":"Dominant combiné","rules":{"r1":{"enabled":false,"need":1,"mode":"relais","offset":5},"r2":{"enabled":false,"need":1,"mode":"relais","offset":5},"r3":{"enabled":false,"need":1,"mode":"relais","offset":5},"perdue":{"enabled":false,"need":1,"mode":"relais","offset":5}},"channels":[],"format":null,"streakKind":"r0","armed":false,"armedKind":null,"sentCount":0,"lastSentAt":null,"createdAt":1788819278031},{"id":"ct-1788813649566-nybwr","key":"after:al-1","name":"Après perte — Costume suivi","rules":{"r1":{"enabled":false,"need":1,"mode":"relais","offset":5},"r2":{"enabled":false,"need":1,"mode":"relais","offset":5},"r3":{"enabled":false,"need":1,"mode":"relais","offset":5},"perdue":{"enabled":true,"need":1,"mode":"relais","offset":5}},"channels":[],"format":null,"streakKind":null,"armed":false,"armedKind":null,"sentCount":0,"lastSentAt":null,"createdAt":1788813649566}],"history":[],"sentCount":0,"lastSentAt":null}</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>combined</v>
+        <v>suitStreak</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="str">
-        <v>{"config":{"enabled":true,"channels":[],"format":1,"maxR":1},"trackers":[{"id":"ct-1","key":"dominant","name":"Dominant combiné","rules":{"r1":{"enabled":false,"need":1,"mode":"relais","offset":5},"r2":{"enabled":false,"need":1,"mode":"relais","offset":5},"r3":{"enabled":false,"need":1,"mode":"relais","offset":5},"perdue":{"enabled":false,"need":1,"mode":"relais","offset":5}},"channels":[],"format":null,"streakKind":"r2","armed":false,"armedKind":null,"sentCount":0,"lastSentAt":null,"createdAt":1788819278031},{"id":"ct-1788813649566-nybwr","key":"after:al-1","name":"Après perte — Costume suivi","rules":{"r1":{"enabled":false,"need":1,"mode":"relais","offset":5},"r2":{"enabled":false,"need":1,"mode":"relais","offset":5},"r3":{"enabled":false,"need":1,"mode":"relais","offset":5},"perdue":{"enabled":true,"need":1,"mode":"relais","offset":5}},"channels":[],"format":null,"streakKind":null,"armed":false,"armedKind":null,"sentCount":0,"lastSentAt":null,"createdAt":1788813649566}],"history":[],"sentCount":0,"lastSentAt":null}</v>
+        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"format":1,"maxR":1},"trackers":[{"id":"ss-1790757310081-ib3m7","key":"dizaine","name":"Ba","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"mirror","channels":[-1004387601010],"siteChannelId":null,"format":88,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":133,"lastSentAt":1791191977631,"createdAt":1790757310081},{"id":"ss-1790760311676-hzdyb","key":"ombreJoueur","name":"Ba2","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"mirror","channels":[-1004387601010],"siteChannelId":null,"format":89,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":122,"lastSentAt":1791192247577,"createdAt":1790760311676},{"id":"ss-1790767126565-8axez","key":"ombreJoueur","name":"Bh1","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"same","channels":[-1004449983073],"siteChannelId":null,"format":90,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":117,"lastSentAt":1791192247565,"createdAt":1790767126565},{"id":"ss-1790767167965-y1oz4","key":"dizaine","name":"Bh2","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"same","channels":[-1004449983073],"siteChannelId":null,"format":91,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":114,"lastSentAt":1791191978055,"createdAt":1790767167965}],"history":[{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":569,"suit":"♠️","sourceTarget":569,"sentAt":1791192247577},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":569,"suit":"♣️","sourceTarget":569,"sentAt":1791192247565},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":564,"suit":"♠️","sourceTarget":564,"sentAt":1791191978055},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":564,"suit":"♣️","sourceTarget":564,"sentAt":1791191977631},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":534,"suit":"♣️","sourceTarget":534,"sentAt":1791190203356},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":534,"suit":"♠️","sourceTarget":534,"sentAt":1791190203356},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":520,"suit":"♦️","sourceTarget":520,"sentAt":1791189312393},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":520,"suit":"❤️","sourceTarget":520,"sentAt":1791189312367},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":484,"suit":"❤️","sourceTarget":484,"sentAt":1791187202683},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":464,"suit":"♣️","sourceTarget":464,"sentAt":1791185947761},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":444,"suit":"♠️","sourceTarget":444,"sentAt":1791184747690},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":432,"suit":"♠️","sourceTarget":432,"sentAt":1791184057558},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":432,"suit":"♣️","sourceTarget":432,"sentAt":1791184057558},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":394,"suit":"❤️","sourceTarget":394,"sentAt":1791181802298},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":394,"suit":"♦️","sourceTarget":394,"sentAt":1791181802293},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":364,"suit":"♦️","sourceTarget":364,"sentAt":1791180002350},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":364,"suit":"❤️","sourceTarget":364,"sentAt":1791180002350},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":358,"suit":"♦️","sourceTarget":358,"sentAt":1791179587451},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":349,"suit":"♠️","sourceTarget":349,"sentAt":1791179047566},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":342,"suit":"♣️","sourceTarget":342,"sentAt":1791178651302},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":324,"suit":"♦️","sourceTarget":324,"sentAt":1791177601369},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":314,"suit":"❤️","sourceTarget":314,"sentAt":1791176976974},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":284,"suit":"❤️","sourceTarget":284,"sentAt":1791175207003},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":234,"suit":"♣️","sourceTarget":234,"sentAt":1791172176796},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":234,"suit":"♠️","sourceTarget":234,"sentAt":1791172176795},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":211,"suit":"♣️","sourceTarget":211,"sentAt":1791170826179},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":211,"suit":"♠️","sourceTarget":211,"sentAt":1791170826176},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":174,"suit":"♠️","sourceTarget":174,"sentAt":1791168606198},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":174,"suit":"♣️","sourceTarget":174,"sentAt":1791168606186},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":144,"suit":"♠️","sourceTarget":144,"sentAt":1791166806054},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":144,"suit":"♣️","sourceTarget":144,"sentAt":1791166806049},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":104,"suit":"♠️","sourceTarget":104,"sentAt":1791164405816},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":104,"suit":"♣️","sourceTarget":104,"sentAt":1791164405783},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":104,"suit":"❤️","sourceTarget":104,"sentAt":1791164405783},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":94,"suit":"♦️","sourceTarget":94,"sentAt":1791163805790},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":66,"suit":"♠️","sourceTarget":66,"sentAt":1791162065679},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":66,"suit":"♣️","sourceTarget":66,"sentAt":1791162065666}],"sentCount":641,"lastSentAt":1791192247577,"channelTitles":{"-1004449983073":"VIP PRENUIM"}}</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>suitStreak</v>
+        <v>dizaineTop</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"format":1,"maxR":1},"trackers":[{"id":"ss-1790757310081-ib3m7","key":"dizaine","name":"Ba","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"mirror","channels":[-1004387601010],"siteChannelId":null,"format":88,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":121,"lastSentAt":1791152380801,"createdAt":1790757310081},{"id":"ss-1790760311676-hzdyb","key":"ombreJoueur","name":"Ba2","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"mirror","channels":[-1004387601010],"siteChannelId":null,"format":89,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":114,"lastSentAt":1791152230784,"createdAt":1790760311676},{"id":"ss-1790767126565-8axez","key":"ombreJoueur","name":"Bh1","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"same","channels":[-1004449983073],"siteChannelId":null,"format":90,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":110,"lastSentAt":1791152231376,"createdAt":1790767126565},{"id":"ss-1790767167965-y1oz4","key":"dizaine","name":"Bh2","n":2,"mode":"next","offset":1,"suitFilter":null,"predictSuit":"same","channels":[-1004449983073],"siteChannelId":null,"format":91,"maxR":3,"streakHasLoss":false,"waitingSuit":null,"mirrorPending":null,"diffPending":null,"sentCount":104,"lastSentAt":1791152380794,"createdAt":1790767167965}],"history":[{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1344,"suit":"♦️","sourceTarget":1344,"sentAt":1791152380801},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1344,"suit":"❤️","sourceTarget":1344,"sentAt":1791152380794},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1342,"suit":"❤️","sourceTarget":1342,"sentAt":1791152231376},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1342,"suit":"♦️","sourceTarget":1342,"sentAt":1791152230784},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1314,"suit":"♣️","sourceTarget":1314,"sentAt":1791150550766},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1314,"suit":"♠️","sourceTarget":1314,"sentAt":1791150550479},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1244,"suit":"❤️","sourceTarget":1244,"sentAt":1791146379818},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1239,"suit":"♦️","sourceTarget":1239,"sentAt":1791146080141},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1239,"suit":"❤️","sourceTarget":1239,"sentAt":1791146080118},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1224,"suit":"♦️","sourceTarget":1224,"sentAt":1791145144706},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1204,"suit":"♦️","sourceTarget":1204,"sentAt":1791143944772},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1199,"suit":"❤️","sourceTarget":1199,"sentAt":1791143704784},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1199,"suit":"♦️","sourceTarget":1199,"sentAt":1791143704784},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1194,"suit":"❤️","sourceTarget":1194,"sentAt":1791143404767},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1164,"suit":"♦️","sourceTarget":1164,"sentAt":1791141549856},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1164,"suit":"❤️","sourceTarget":1164,"sentAt":1791141549494},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1128,"suit":"♦️","sourceTarget":1128,"sentAt":1791139419286},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1128,"suit":"❤️","sourceTarget":1128,"sentAt":1791139418958},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1104,"suit":"♣️","sourceTarget":1104,"sentAt":1791138003819},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1104,"suit":"♠️","sourceTarget":1104,"sentAt":1791138003803},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1102,"suit":"♠️","sourceTarget":1102,"sentAt":1791137883411},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1102,"suit":"♣️","sourceTarget":1102,"sentAt":1791137883410},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1064,"suit":"♦️","sourceTarget":1064,"sentAt":1791135603582},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1056,"suit":"♦️","sourceTarget":1056,"sentAt":1791135093362},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1056,"suit":"❤️","sourceTarget":1056,"sentAt":1791135093351},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1054,"suit":"❤️","sourceTarget":1054,"sentAt":1791134953841},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1024,"suit":"♦️","sourceTarget":1024,"sentAt":1791133208172},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1014,"suit":"❤️","sourceTarget":1014,"sentAt":1791132548308},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1011,"suit":"♦️","sourceTarget":1011,"sentAt":1791132424083},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1011,"suit":"❤️","sourceTarget":1011,"sentAt":1791132423696},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":964,"suit":"♦️","sourceTarget":964,"sentAt":1791129552545},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":954,"suit":"❤️","sourceTarget":954,"sentAt":1791128952410},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":953,"suit":"❤️","sourceTarget":953,"sentAt":1791128942642},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":953,"suit":"♦️","sourceTarget":953,"sentAt":1791128942525},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":905,"suit":"♣️","sourceTarget":905,"sentAt":1791126007486},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":905,"suit":"♠️","sourceTarget":905,"sentAt":1791126007480},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":894,"suit":"♣️","sourceTarget":894,"sentAt":1791125352316},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":874,"suit":"❤️","sourceTarget":874,"sentAt":1791124207423},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":864,"suit":"♦️","sourceTarget":864,"sentAt":1791123577647},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":756,"suit":"♣️","sourceTarget":756,"sentAt":1791117097402},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":754,"suit":"♠️","sourceTarget":754,"sentAt":1791116982358},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":734,"suit":"♠️","sourceTarget":734,"sentAt":1791115806884},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":734,"suit":"♣️","sourceTarget":734,"sentAt":1791115806884},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":732,"suit":"♠️","sourceTarget":732,"sentAt":1791115656641},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":732,"suit":"♣️","sourceTarget":732,"sentAt":1791115656334},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":684,"suit":"♠️","sourceTarget":684,"sentAt":1791112746474},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":684,"suit":"♣️","sourceTarget":684,"sentAt":1791112746269},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":654,"suit":"♦️","sourceTarget":654,"sentAt":1791111006023},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":654,"suit":"❤️","sourceTarget":654,"sentAt":1791111006002},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":648,"suit":"❤️","sourceTarget":648,"sentAt":1791110646015},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":648,"suit":"♦️","sourceTarget":648,"sentAt":1791110645701},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":624,"suit":"♣️","sourceTarget":624,"sentAt":1791109206456},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":624,"suit":"♠️","sourceTarget":624,"sentAt":1791109205884},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":604,"suit":"❤️","sourceTarget":604,"sentAt":1791108005929},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":604,"suit":"♦️","sourceTarget":604,"sentAt":1791108005613},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":544,"suit":"❤️","sourceTarget":544,"sentAt":1791104404807},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":544,"suit":"♦️","sourceTarget":544,"sentAt":1791104404804},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":537,"suit":"♦️","sourceTarget":537,"sentAt":1791103985714},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":537,"suit":"❤️","sourceTarget":537,"sentAt":1791103985084},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":486,"suit":"❤️","sourceTarget":486,"sentAt":1791100870036},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":486,"suit":"♦️","sourceTarget":486,"sentAt":1791100869740},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":451,"suit":"♦️","sourceTarget":451,"sentAt":1791098829683},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":451,"suit":"❤️","sourceTarget":451,"sentAt":1791098829583},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":424,"suit":"♦️","sourceTarget":424,"sentAt":1791097149408},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":414,"suit":"❤️","sourceTarget":414,"sentAt":1791096578713},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":384,"suit":"♦️","sourceTarget":384,"sentAt":1791094749084},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":374,"suit":"❤️","sourceTarget":374,"sentAt":1791094208312},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":366,"suit":"♠️","sourceTarget":366,"sentAt":1791093723503},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":366,"suit":"♣️","sourceTarget":366,"sentAt":1791093723251},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":334,"suit":"♦️","sourceTarget":334,"sentAt":1791091773670},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":334,"suit":"❤️","sourceTarget":334,"sentAt":1791091773213},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":254,"suit":"♦️","sourceTarget":254,"sentAt":1791087007426},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":248,"suit":"♦️","sourceTarget":248,"sentAt":1791086587719},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":248,"suit":"❤️","sourceTarget":248,"sentAt":1791086587718},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":244,"suit":"❤️","sourceTarget":244,"sentAt":1791086347884},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":204,"suit":"♦️","sourceTarget":204,"sentAt":1791083947187},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":204,"suit":"❤️","sourceTarget":204,"sentAt":1791083947183},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":199,"suit":"❤️","sourceTarget":199,"sentAt":1791083676816},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":199,"suit":"♦️","sourceTarget":199,"sentAt":1791083676803},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":174,"suit":"❤️","sourceTarget":174,"sentAt":1791082172110},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":145,"suit":"❤️","sourceTarget":145,"sentAt":1791080412220},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":145,"suit":"♦️","sourceTarget":145,"sentAt":1791080411977},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":110,"suit":"♦️","sourceTarget":110,"sentAt":1791078337430},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":110,"suit":"❤️","sourceTarget":110,"sentAt":1791078337112},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":58,"suit":"♣️","sourceTarget":58,"sentAt":1791075218809},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":58,"suit":"♠️","sourceTarget":58,"sentAt":1791075216792},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":34,"suit":"♦️","sourceTarget":34,"sentAt":1791073746921},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":34,"suit":"❤️","sourceTarget":34,"sentAt":1791073746618},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1410,"suit":"♣️","sourceTarget":1410,"sentAt":1791069936398},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1410,"suit":"♠️","sourceTarget":1410,"sentAt":1791069936394},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1404,"suit":"♦️","sourceTarget":1404,"sentAt":1791069576190},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1394,"suit":"❤️","sourceTarget":1394,"sentAt":1791068951127},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1360,"suit":"♠️","sourceTarget":1360,"sentAt":1791066966345},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1360,"suit":"♣️","sourceTarget":1360,"sentAt":1791066966069},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1333,"suit":"♣️","sourceTarget":1333,"sentAt":1791065315227},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1333,"suit":"♠️","sourceTarget":1333,"sentAt":1791065315221},{"trackerId":"ss-1790767167965-y1oz4","trackerName":"Bh2","target":1324,"suit":"❤️","sourceTarget":1324,"sentAt":1791064776273},{"trackerId":"ss-1790757310081-ib3m7","trackerName":"Ba","target":1324,"suit":"♦️","sourceTarget":1324,"sentAt":1791064775783},{"trackerId":"ss-1790767126565-8axez","trackerName":"Bh1","target":1294,"suit":"♣️","sourceTarget":1294,"sentAt":1791063006245},{"trackerId":"ss-1790760311676-hzdyb","trackerName":"Ba2","target":1294,"suit":"♠️","sourceTarget":1294,"sentAt":1791063005367}],"sentCount":604,"lastSentAt":1791152380801,"channelTitles":{"-1004449983073":"VIP PRENUIM"}}</v>
+        <v>{"config":{"enabled":true},"trackers":[{"id":"dt-1791190012546-m5b9w","mode":"plus","rank":1,"lead":4,"enabled":true,"channels":[-1003932129001],"siteChannelId":null,"format":3,"maxR":3,"lastDecade":570,"lastInfo":{"start":561,"end":570,"readable":10,"counts":{"♦️":5,"❤️":6,"♣️":4,"♠️":4},"suit":"❤️","target":574,"at":1791192577218},"wins":5,"losses":0,"sentCount":5,"lastSentAt":1791192577751,"createdAt":1791190012546,"name":"Bot1"},{"id":"dt-1791190058355-h6bfc","mode":"plus","rank":2,"lead":4,"enabled":true,"channels":[-1003991686866],"siteChannelId":null,"format":3,"maxR":3,"lastDecade":570,"lastInfo":{"start":561,"end":570,"readable":10,"counts":{"♦️":5,"❤️":6,"♣️":4,"♠️":4},"suit":"♦️","target":574,"at":1791192577757},"wins":5,"losses":0,"sentCount":5,"lastSentAt":1791192578110,"createdAt":1791190058355,"name":"Bot2"},{"id":"dt-1791190095860-jlt07","mode":"plus","rank":3,"lead":4,"enabled":true,"channels":[-1004368493318],"siteChannelId":null,"format":3,"maxR":3,"lastDecade":570,"lastInfo":{"start":561,"end":570,"readable":10,"counts":{"♦️":5,"❤️":6,"♣️":4,"♠️":4},"suit":"♣️","target":574,"at":1791192578111},"wins":4,"losses":1,"sentCount":5,"lastSentAt":1791192578345,"createdAt":1791190095860,"name":"Bot3"}],"history":[{"trackerId":"dt-1791190095860-jlt07","trackerName":"Bot3","target":574,"suit":"♣️","detail":"#N561-#N570 ♦️:5 ❤️:6 ♣️:4 ♠️:4","sentAt":1791192578345},{"trackerId":"dt-1791190058355-h6bfc","trackerName":"Bot2","target":574,"suit":"♦️","detail":"#N561-#N570 ♦️:5 ❤️:6 ♣️:4 ♠️:4","sentAt":1791192578110},{"trackerId":"dt-1791190012546-m5b9w","trackerName":"Bot1","target":574,"suit":"❤️","detail":"#N561-#N570 ♦️:5 ❤️:6 ♣️:4 ♠️:4","sentAt":1791192577751},{"trackerId":"dt-1791190095860-jlt07","trackerName":"Bot3","target":564,"suit":"♠️","detail":"#N551-#N560 ♦️:5 ❤️:5 ♣️:4 ♠️:5","sentAt":1791191978551},{"trackerId":"dt-1791190058355-h6bfc","trackerName":"Bot2","target":564,"suit":"❤️","detail":"#N551-#N560 ♦️:5 ❤️:5 ♣️:4 ♠️:5","sentAt":1791191978322},{"trackerId":"dt-1791190012546-m5b9w","trackerName":"Bot1","target":564,"suit":"♦️","detail":"#N551-#N560 ♦️:5 ❤️:5 ♣️:4 ♠️:5","sentAt":1791191978067},{"trackerId":"dt-1791190095860-jlt07","trackerName":"Bot3","target":554,"suit":"♣️","detail":"#N541-#N550 ♦️:7 ❤️:7 ♣️:3 ♠️:2","sentAt":1791191403634},{"trackerId":"dt-1791190058355-h6bfc","trackerName":"Bot2","target":554,"suit":"❤️","detail":"#N541-#N550 ♦️:7 ❤️:7 ♣️:3 ♠️:2","sentAt":1791191403379},{"trackerId":"dt-1791190012546-m5b9w","trackerName":"Bot1","target":554,"suit":"♦️","detail":"#N541-#N550 ♦️:7 ❤️:7 ♣️:3 ♠️:2","sentAt":1791191403123},{"trackerId":"dt-1791190095860-jlt07","trackerName":"Bot3","target":544,"suit":"♣️","detail":"#N531-#N540 ♦️:5 ❤️:6 ♣️:5 ♠️:3","sentAt":1791190782977},{"trackerId":"dt-1791190058355-h6bfc","trackerName":"Bot2","target":544,"suit":"♦️","detail":"#N531-#N540 ♦️:5 ❤️:6 ♣️:5 ♠️:3","sentAt":1791190782738},{"trackerId":"dt-1791190012546-m5b9w","trackerName":"Bot1","target":544,"suit":"❤️","detail":"#N531-#N540 ♦️:5 ❤️:6 ♣️:5 ♠️:3","sentAt":1791190782509},{"trackerId":"dt-1791190095860-jlt07","trackerName":"Bot3","target":534,"suit":"♣️","detail":"#N521-#N530 ♦️:2 ❤️:5 ♣️:4 ♠️:9","sentAt":1791190204225},{"trackerId":"dt-1791190058355-h6bfc","trackerName":"Bot2","target":534,"suit":"❤️","detail":"#N521-#N530 ♦️:2 ❤️:5 ♣️:4 ♠️:9","sentAt":1791190203973},{"trackerId":"dt-1791190012546-m5b9w","trackerName":"Bot1","target":534,"suit":"♠️","detail":"#N521-#N530 ♦️:2 ❤️:5 ♣️:4 ♠️:9","sentAt":1791190203743},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":524,"suit":"♠️","detail":"#N511-#N520 ♦️:5 ❤️:5 ♣️:3 ♠️:6","sentAt":1791189572980},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":514,"suit":"♠️","detail":"#N501-#N510 ♦️:5 ❤️:5 ♣️:4 ♠️:7","sentAt":1791188947928},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":504,"suit":"♣️","detail":"#N491-#N500 ♦️:7 ❤️:1 ♣️:8 ♠️:3","sentAt":1791188348125},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":494,"suit":"♣️","detail":"#N481-#N490 ♦️:4 ❤️:5 ♣️:6 ♠️:6","sentAt":1791187802864},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":484,"suit":"♣️","detail":"#N471-#N480 ♦️:5 ❤️:5 ♣️:6 ♠️:4","sentAt":1791187202679},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":474,"suit":"♣️","detail":"#N461-#N470 ♦️:3 ❤️:5 ♣️:6 ♠️:5","sentAt":1791186582392},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":464,"suit":"❤️","detail":"#N451-#N460 ♦️:4 ❤️:6 ♣️:5 ♠️:5","sentAt":1791185947766},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":454,"suit":"♠️","detail":"#N441-#N450 ♦️:5 ❤️:5 ♣️:3 ♠️:6","sentAt":1791185352076},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":444,"suit":"❤️","detail":"#N431-#N440 ♦️:6 ❤️:8 ♣️:4 ♠️:7","sentAt":1791184747693},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":434,"suit":"❤️","detail":"#N421-#N430 ♦️:4 ❤️:7 ♣️:3 ♠️:7","sentAt":1791184147466},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":424,"suit":"♦️","detail":"#N411-#N420 ♦️:8 ❤️:5 ♣️:3 ♠️:4","sentAt":1791183607464},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":414,"suit":"♣️","detail":"#N401-#N410 ♦️:5 ❤️:4 ♣️:6 ♠️:6","sentAt":1791182952452},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":404,"suit":"♣️","detail":"#N391-#N400 ♦️:2 ❤️:5 ♣️:6 ♠️:5","sentAt":1791182372658},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":394,"suit":"♦️","detail":"#N381-#N390 ♦️:6 ❤️:5 ♣️:6 ♠️:3","sentAt":1791181802287},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":384,"suit":"❤️","detail":"#N371-#N380 ♦️:4 ❤️:7 ♣️:4 ♠️:6","sentAt":1791181151776},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":374,"suit":"♠️","detail":"#N361-#N370 ♦️:3 ❤️:3 ♣️:6 ♠️:7","sentAt":1791180572178},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":364,"suit":"❤️","detail":"#N351-#N360 ♦️:4 ❤️:6 ♣️:4 ♠️:4","sentAt":1791180002162},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":354,"suit":"♣️","detail":"#N341-#N350 ♦️:5 ❤️:2 ♣️:6 ♠️:5","sentAt":1791179347068},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":344,"suit":"♦️","detail":"#N331-#N340 ♦️:8 ❤️:4 ♣️:5 ♠️:4","sentAt":1791178777179},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":334,"suit":"❤️","detail":"#N321-#N330 ♦️:4 ❤️:7 ♣️:6 ♠️:4","sentAt":1791178206974},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":324,"suit":"♣️","detail":"#N311-#N320 ♦️:5 ❤️:4 ♣️:9 ♠️:4","sentAt":1791177601373},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":314,"suit":"♣️","detail":"#N301-#N310 ♦️:3 ❤️:4 ♣️:9 ♠️:6","sentAt":1791176976959},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":304,"suit":"♠️","detail":"#N291-#N300 ♦️:3 ❤️:5 ♣️:3 ♠️:7","sentAt":1791176346876},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":294,"suit":"❤️","detail":"#N281-#N290 ♦️:4 ❤️:7 ♣️:7 ♠️:6","sentAt":1791175746751},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":284,"suit":"❤️","detail":"#N271-#N280 ♦️:5 ❤️:6 ♣️:5 ♠️:6","sentAt":1791175206985},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":274,"suit":"♣️","detail":"#N261-#N270 ♦️:4 ❤️:6 ♣️:7 ♠️:7","sentAt":1791174576709},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":264,"suit":"❤️","detail":"#N251-#N260 ♦️:4 ❤️:5 ♣️:5 ♠️:4","sentAt":1791173946568},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":254,"suit":"♠️","detail":"#N241-#N250 ♦️:5 ❤️:4 ♣️:2 ♠️:9","sentAt":1791173406857},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":244,"suit":"♣️","detail":"#N231-#N240 ♦️:4 ❤️:2 ♣️:9 ♠️:3","sentAt":1791172751472},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":234,"suit":"♣️","detail":"#N221-#N230 ♦️:5 ❤️:5 ♣️:7 ♠️:4","sentAt":1791172177117},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":224,"suit":"♦️","detail":"#N211-#N220 ♦️:6 ❤️:6 ♣️:3 ♠️:5","sentAt":1791171546718},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":214,"suit":"♦️","detail":"#N201-#N210 ♦️:8 ❤️:5 ♣️:3 ♠️:7","sentAt":1791170976556},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":204,"suit":"♦️","detail":"#N191-#N200 ♦️:6 ❤️:5 ♣️:6 ♠️:4","sentAt":1791170406661},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":194,"suit":"♣️","detail":"#N181-#N190 ♦️:3 ❤️:5 ♣️:8 ♠️:3","sentAt":1791169746351},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":184,"suit":"♦️","detail":"#N171-#N180 ♦️:7 ❤️:4 ♣️:7 ♠️:5","sentAt":1791169146754},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":174,"suit":"♠️","detail":"#N161-#N170 ♦️:1 ❤️:4 ♣️:6 ♠️:7","sentAt":1791168606207},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":164,"suit":"♦️","detail":"#N151-#N160 ♦️:7 ❤️:5 ♣️:6 ♠️:2","sentAt":1791167976450},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":154,"suit":"♣️","detail":"#N141-#N150 ♦️:4 ❤️:5 ♣️:6 ♠️:3","sentAt":1791167351161},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":144,"suit":"♦️","detail":"#N131-#N140 ♦️:7 ❤️:5 ♣️:7 ♠️:5","sentAt":1791166806039},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":134,"suit":"♦️","detail":"#N121-#N130 ♦️:8 ❤️:3 ♣️:1 ♠️:8","sentAt":1791166206036},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":124,"suit":"♦️","detail":"#N111-#N120 ♦️:5 ❤️:5 ♣️:3 ♠️:5","sentAt":1791165551098},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":114,"suit":"♦️","detail":"#N101-#N110 ♦️:6 ❤️:4 ♣️:6 ♠️:5","sentAt":1791164951152},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":104,"suit":"♣️","detail":"#N91-#N100 ♦️:5 ❤️:5 ♣️:6 ♠️:3","sentAt":1791164406169},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":94,"suit":"♦️","detail":"#N81-#N90 ♦️:7 ❤️:3 ♣️:5 ♠️:3","sentAt":1791163805785},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":84,"suit":"♣️","detail":"#N71-#N80 ♦️:4 ❤️:2 ♣️:9 ♠️:4","sentAt":1791163145767},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":74,"suit":"♦️","detail":"#N61-#N70 ♦️:6 ❤️:4 ♣️:5 ♠️:5","sentAt":1791162550690},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":64,"suit":"♦️","detail":"#N51-#N60 ♦️:9 ❤️:6 ♣️:1 ♠️:5","sentAt":1791161976259},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":54,"suit":"♣️","detail":"#N41-#N50 ♦️:6 ❤️:5 ♣️:8 ♠️:2","sentAt":1791161376050},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":44,"suit":"♦️","detail":"#N31-#N40 ♦️:7 ❤️:4 ♣️:6 ♠️:5","sentAt":1791160805777},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":34,"suit":"♠️","detail":"#N21-#N30 ♦️:3 ❤️:4 ♣️:6 ♠️:7","sentAt":1791160145906},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":24,"suit":"♠️","detail":"#N11-#N20 ♦️:5 ❤️:4 ♣️:5 ♠️:6","sentAt":1791159605486},{"trackerId":"dt-1791157972323-55v4y","trackerName":"-1004411440341","target":14,"suit":"♦️","detail":"#N1-#N10 ♦️:9 ❤️:6 ♣️:5 ♠️:4","sentAt":1791158975540}],"sentCount":67,"lastSentAt":1791192578345,"channelTitles":{"-1004411440341":"Stratégie solide Baccara","-1003932129001":"Bot 1","-1003991686866":"Bot 2","-1004368493318":"Bot3"}}</v>
       </c>
     </row>
     <row r="7">
@@ -2432,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"format":1,"maxR":1},"trackers":[{"id":"sb-1789498464258-iqnmx","key":"costume","name":"Costume par numéro","n":2,"channels":[-100123],"siteChannelId":null,"format":null,"maxR":1,"seen":[{"target":1356,"suit":"♣️","status":"en attente","note":"nouvelle série ♣️ ×1","at":1791153105212},{"target":1355,"suit":"❤️","status":"en attente","note":"nouvelle série ❤️ ×1","at":1791153105212},{"target":1352,"suit":"♦️","status":"en attente","note":"nouvelle série ♦️ ×1","at":1791153105212},{"target":1349,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791153105212},{"target":1346,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791153105212},{"target":1345,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791153105212},{"target":1342,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791153105212},{"target":1339,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791153105212},{"target":1336,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791153105212},{"target":1332,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791153105212},{"target":1329,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791153105212},{"target":1326,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791153105212},{"target":1325,"suit":"❤️","status":"perdu","note":"nouvelle série ❤️ ×1","at":1791153105212},{"target":1322,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791153105212},{"target":1319,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791153105212},{"target":1316,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791153105212},{"target":1315,"suit":"❤️","status":"perdu","note":"nouvelle série ❤️ ×1","at":1791153105212},{"target":1312,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791153105212},{"target":1309,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791153105212},{"target":1306,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791153105212},{"target":1305,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791153105212},{"target":1302,"suit":"♦️","status":"perdu","note":"nouvelle série ♦️ ×1","at":1791153105212},{"target":1299,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791153105212},{"target":1296,"suit":"♣️","status":"perdu","note":"nouvelle série ♣️ ×1","at":1791153105212},{"target":1295,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791153105212}],"readCount":1191622,"fireCount":0,"lastFireAt":null,"sentCount":0,"lastSentAt":null,"createdAt":1789498464258}],"history":[],"sentCount":0,"lastSentAt":null,"sentFingerprints":[],"channelTitles":{}}</v>
+        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"format":1,"maxR":1},"trackers":[{"id":"sb-1789498464258-iqnmx","key":"costume","name":"Costume par numéro","n":2,"channels":[-100123],"siteChannelId":null,"format":null,"maxR":1,"seen":[{"target":582,"suit":"♦️","status":"en attente","note":"nouvelle série ♦️ ×1","at":1791193027022},{"target":579,"suit":"♠️","status":"en attente","note":"nouvelle série ♠️ ×1","at":1791193027022},{"target":576,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791193027022},{"target":575,"suit":"❤️","status":"perdu","note":"nouvelle série ❤️ ×1","at":1791193027022},{"target":572,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791193027022},{"target":569,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791193027022},{"target":566,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791193027022},{"target":565,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791193027022},{"target":562,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791193027022},{"target":559,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791193027022},{"target":556,"suit":"♣️","status":"perdu","note":"nouvelle série ♣️ ×1","at":1791193027022},{"target":555,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791193027022},{"target":552,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791193027022},{"target":549,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791193027022},{"target":546,"suit":"♣️","status":"perdu","note":"nouvelle série ♣️ ×1","at":1791193027022},{"target":545,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791193027022},{"target":542,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791193027022},{"target":539,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791193027022},{"target":536,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791193027022},{"target":535,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791193027022},{"target":532,"suit":"♦️","status":"gagné","note":"nouvelle série ♦️ ×1","at":1791193027022},{"target":529,"suit":"♠️","status":"gagné","note":"nouvelle série ♠️ ×1","at":1791193027022},{"target":526,"suit":"♣️","status":"gagné","note":"nouvelle série ♣️ ×1","at":1791193027022},{"target":525,"suit":"❤️","status":"gagné","note":"nouvelle série ❤️ ×1","at":1791193027022},{"target":522,"suit":"♦️","status":"perdu","note":"nouvelle série ♦️ ×1","at":1791193027022}],"readCount":434661,"fireCount":0,"lastFireAt":null,"sentCount":0,"lastSentAt":null,"createdAt":1789498464258}],"history":[],"sentCount":0,"lastSentAt":null,"sentFingerprints":[],"channelTitles":{}}</v>
       </c>
     </row>
     <row r="8">
@@ -2454,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="str">
-        <v>{"config":{"enabled":true,"channels":[-1002699763359]},"tracked":{"953":{"messages":[{"chatId":-1002699763359,"messageId":763831}],"signature":"3|3|1|1|1|","finished":true},"954":{"messages":[{"chatId":-1002699763359,"messageId":763832}],"signature":"3|2|9|7|1|Joueur","finished":true},"955":{"messages":[{"chatId":-1002699763359,"messageId":763833}],"signature":"2|2|3|8|1|Banquier","finished":true},"956":{"messages":[{"chatId":-1002699763359,"messageId":763834}],"signature":"2|3|7|0|1|Joueur","finished":true},"957":{"messages":[{"chatId":-1002699763359,"messageId":763835}],"signature":"2|3|7|4|1|Joueur","finished":true},"958":{"messages":[{"chatId":-1002699763359,"messageId":763836}],"signature":"3|3|0|8|1|Banquier","finished":true},"959":{"messages":[{"chatId":-1002699763359,"messageId":763837}],"signature":"3|3|6|9|1|Banquier","finished":true},"960":{"messages":[{"chatId":-1002699763359,"messageId":763838}],"signature":"2|2|0|8|1|Banquier","finished":true},"961":{"messages":[{"chatId":-1002699763359,"messageId":763839}],"signature":"3|2|8|6|1|Joueur","finished":true},"962":{"messages":[{"chatId":-1002699763359,"messageId":763840}],"signature":"2|2|9|5|1|Joueur","finished":true},"963":{"messages":[{"chatId":-1002699763359,"messageId":763841}],"signature":"2|2|1|8|1|Banquier","finished":true},"964":{"messages":[{"chatId":-1002699763359,"messageId":763842}],"signature":"2|2|7|6|1|Joueur","finished":true},"965":{"messages":[{"chatId":-1002699763359,"messageId":763843}],"signature":"3|2|2|6|1|Banquier","finished":true},"966":{"messages":[{"chatId":-1002699763359,"messageId":763844}],"signature":"2|2|9|3|1|Joueur","finished":true},"967":{"messages":[{"chatId":-1002699763359,"messageId":763845}],"signature":"3|3|1|9|1|Banquier","finished":true},"968":{"messages":[{"chatId":-1002699763359,"messageId":763846}],"signature":"2|2|8|0|1|Joueur","finished":true},"969":{"messages":[{"chatId":-1002699763359,"messageId":763847}],"signature":"3|2|3|4|1|Banquier","finished":true},"970":{"messages":[{"chatId":-1002699763359,"messageId":763848}],"signature":"2|2|8|6|1|Joueur","finished":true},"971":{"messages":[{"chatId":-1002699763359,"messageId":763849}],"signature":"3|2|5|5|1|","finished":true},"972":{"messages":[{"chatId":-1002699763359,"messageId":763850}],"signature":"2|2|2|8|1|Banquier","finished":true},"973":{"messages":[{"chatId":-1002699763359,"messageId":763851}],"signature":"3|3|3|8|1|Banquier","finished":true},"974":{"messages":[{"chatId":-1002699763359,"messageId":763852}],"signature":"2|2|8|0|1|Joueur","finished":true},"975":{"messages":[{"chatId":-1002699763359,"messageId":763853}],"signature":"3|3|6|9|1|Banquier","finished":true},"976":{"messages":[{"chatId":-1002699763359,"messageId":763854}],"signature":"2|2|6|7|1|Banquier","finished":true},"977":{"messages":[{"chatId":-1002699763359,"messageId":763855}],"signature":"2|2|7|9|1|Banquier","finished":true},"978":{"messages":[{"chatId":-1002699763359,"messageId":763856}],"signature":"2|2|2|9|1|Banquier","finished":true},"979":{"messages":[{"chatId":-1002699763359,"messageId":763857}],"signature":"3|3|1|2|1|Banquier","finished":true},"980":{"messages":[{"chatId":-1002699763359,"messageId":763858}],"signature":"2|2|3|9|1|Banquier","finished":true},"981":{"messages":[{"chatId":-1002699763359,"messageId":763859}],"signature":"2|2|7|8|1|Banquier","finished":true},"982":{"messages":[{"chatId":-1002699763359,"messageId":763860}],"signature":"2|2|9|7|1|Joueur","finished":true},"983":{"messages":[{"chatId":-1002699763359,"messageId":763861}],"signature":"3|3|6|1|1|Joueur","finished":true},"984":{"messages":[{"chatId":-1002699763359,"messageId":763862}],"signature":"3|3|2|4|1|Banquier","finished":true},"985":{"messages":[{"chatId":-1002699763359,"messageId":763863}],"signature":"2|3|6|2|1|Joueur","finished":true},"986":{"messages":[{"chatId":-1002699763359,"messageId":763864}],"signature":"3|2|0|4|1|Banquier","finished":true},"987":{"messages":[{"chatId":-1002699763359,"messageId":763865}],"signature":"2|3|6|8|1|Banquier","finished":true},"988":{"messages":[{"chatId":-1002699763359,"messageId":763866}],"signature":"2|2|8|8|1|","finished":true},"989":{"messages":[{"chatId":-1002699763359,"messageId":763867}],"signature":"3|3|1|2|1|Banquier","finished":true},"990":{"messages":[{"chatId":-1002699763359,"messageId":763868}],"signature":"2|3|7|0|1|Joueur","finished":true},"991":{"messages":[{"chatId":-1002699763359,"messageId":763869}],"signature":"3|3|2|6|1|Banquier","finished":true},"992":{"messages":[{"chatId":-1002699763359,"messageId":763870}],"signature":"2|2|9|6|1|Joueur","finished":true},"993":{"messages":[{"chatId":-1002699763359,"messageId":763871}],"signature":"3|3|2|3|1|Banquier","finished":true},"994":{"messages":[{"chatId":-1002699763359,"messageId":763872}],"signature":"2|2|7|8|1|Banquier","finished":true},"995":{"messages":[{"chatId":-1002699763359,"messageId":763873}],"signature":"2|3|7|3|1|Joueur","finished":true},"996":{"messages":[{"chatId":-1002699763359,"messageId":763874}],"signature":"2|2|4|9|1|Banquier","finished":true},"997":{"messages":[{"chatId":-1002699763359,"messageId":763875}],"signature":"2|2|9|5|1|Joueur","finished":true},"998":{"messages":[{"chatId":-1002699763359,"messageId":763876}],"signature":"3|2|1|4|1|Banquier","finished":true},"999":{"messages":[{"chatId":-1002699763359,"messageId":763877}],"signature":"3|2|2|7|1|Banquier","finished":true},"1000":{"messages":[{"chatId":-1002699763359,"messageId":763878}],"signature":"3|2|9|5|1|Joueur","finished":true},"1001":{"messages":[{"chatId":-1002699763359,"messageId":763879}],"signature":"3|2|2|7|1|Banquier","finished":true},"1002":{"messages":[{"chatId":-1002699763359,"messageId":763880}],"signature":"3|2|1|4|1|Banquier","finished":true},"1003":{"messages":[{"chatId":-1002699763359,"messageId":763881}],"signature":"3|2|0|7|1|Banquier","finished":true},"1004":{"messages":[{"chatId":-1002699763359,"messageId":763882}],"signature":"3|3|9|0|1|Joueur","finished":true},"1005":{"messages":[{"chatId":-1002699763359,"messageId":763883}],"signature":"3|2|1|7|1|Banquier","finished":true},"1006":{"messages":[{"chatId":-1002699763359,"messageId":763884}],"signature":"3|3|4|4|1|","finished":true},"1007":{"messages":[{"chatId":-1002699763359,"messageId":763885}],"signature":"3|3|3|0|1|Joueur","finished":true},"1008":{"messages":[{"chatId":-1002699763359,"messageId":763886}],"signature":"2|2|8|0|1|Joueur","finished":true},"1009":{"messages":[{"chatId":-1002699763359,"messageId":763887}],"signature":"3|3|4|6|1|Banquier","finished":true},"1010":{"messages":[{"chatId":-1002699763359,"messageId":763888}],"signature":"2|2|8|2|1|Joueur","finished":true},"1011":{"messages":[{"chatId":-1002699763359,"messageId":763889}],"signature":"2|3|7|2|1|Joueur","finished":true},"1012":{"messages":[{"chatId":-1002699763359,"messageId":763890}],"signature":"3|3|1|0|1|Joueur","finished":true},"1013":{"messages":[{"chatId":-1002699763359,"messageId":763891}],"signature":"3|3|7|6|1|Joueur","finished":true},"1014":{"messages":[{"chatId":-1002699763359,"messageId":763892}],"signature":"3|2|1|5|1|Banquier","finished":true},"1015":{"messages":[{"chatId":-1002699763359,"messageId":763893}],"signature":"3|2|5|7|1|Banquier","finished":true},"1016":{"messages":[{"chatId":-1002699763359,"messageId":763894}],"signature":"2|3|7|0|1|Joueur","finished":true},"1017":{"messages":[{"chatId":-1002699763359,"messageId":763895}],"signature":"3|3|6|5|1|Joueur","finished":true},"1018":{"messages":[{"chatId":-1002699763359,"messageId":763896}],"signature":"3|2|1|6|1|Banquier","finished":true},"1019":{"messages":[{"chatId":-1002699763359,"messageId":763897}],"signature":"2|2|0|8|1|Banquier","finished":true},"1020":{"messages":[{"chatId":-1002699763359,"messageId":763898}],"signature":"3|3|0|5|1|Banquier","finished":true},"1021":{"messages":[{"chatId":-1002699763359,"messageId":763899}],"signature":"3|2|6|7|1|Banquier","finished":true},"1022":{"messages":[{"chatId":-1002699763359,"messageId":763900}],"signature":"3|2|2|4|1|Banquier","finished":true},"1023":{"messages":[{"chatId":-1002699763359,"messageId":763901}],"signature":"3|3|5|0|1|Joueur","finished":true},"1024":{"messages":[{"chatId":-1002699763359,"messageId":763902}],"signature":"2|2|2|9|1|Banquier","finished":true},"1025":{"messages":[{"chatId":-1002699763359,"messageId":763903}],"signature":"2|3|6|4|1|Joueur","finished":true},"1026":{"messages":[{"chatId":-1002699763359,"messageId":763904}],"signature":"2|2|9|4|1|Joueur","finished":true},"1027":{"messages":[{"chatId":-1002699763359,"messageId":763905}],"signature":"3|2|2|6|1|Banquier","finished":true},"1028":{"messages":[{"chatId":-1002699763359,"messageId":763906}],"signature":"3|3|3|9|1|Banquier","finished":true},"1029":{"messages":[{"chatId":-1002699763359,"messageId":763907}],"signature":"3|3|0|9|1|Banquier","finished":true},"1030":{"messages":[{"chatId":-1002699763359,"messageId":763908}],"signature":"2|2|9|1|1|Joueur","finished":true},"1031":{"messages":[{"chatId":-1002699763359,"messageId":763909}],"signature":"2|3|7|4|1|Joueur","finished":true},"1032":{"messages":[{"chatId":-1002699763359,"messageId":763910}],"signature":"2|3|6|0|1|Joueur","finished":true},"1033":{"messages":[{"chatId":-1002699763359,"messageId":763911}],"signature":"2|3|7|7|1|","finished":true},"1034":{"messages":[{"chatId":-1002699763359,"messageId":763912}],"signature":"3|3|0|1|1|Banquier","finished":true},"1035":{"messages":[{"chatId":-1002699763359,"messageId":763913}],"signature":"3|3|0|9|1|Banquier","finished":true},"1036":{"messages":[{"chatId":-1002699763359,"messageId":763914}],"signature":"2|2|9|0|1|Joueur","finished":true},"1037":{"messages":[{"chatId":-1002699763359,"messageId":763915}],"signature":"2|2|9|6|1|Joueur","finished":true},"1038":{"messages":[{"chatId":-1002699763359,"messageId":763916}],"signature":"3|2|4|4|1|","finished":true},"1039":{"messages":[{"chatId":-1002699763359,"messageId":763917}],"signature":"3|3|5|1|1|Joueur","finished":true},"1040":{"messages":[{"chatId":-1002699763359,"messageId":763918}],"signature":"2|2|2|8|1|Banquier","finished":true},"1041":{"messages":[{"chatId":-1002699763359,"messageId":763919}],"signature":"3|2|2|5|1|Banquier","finished":true},"1042":{"messages":[{"chatId":-1002699763359,"messageId":763920}],"signature":"2|3|6|3|1|Joueur","finished":true},"1043":{"messages":[{"chatId":-1002699763359,"messageId":763921}],"signature":"3|2|3|6|1|Banquier","finished":true},"1044":{"messages":[{"chatId":-1002699763359,"messageId":763922}],"signature":"3|3|9|2|1|Joueur","finished":true},"1045":{"messages":[{"chatId":-1002699763359,"messageId":763923}],"signature":"3|2|7|6|1|Joueur","finished":true},"1046":{"messages":[{"chatId":-1002699763359,"messageId":763924}],"signature":"3|3|4|9|1|Banquier","finished":true},"1047":{"messages":[{"chatId":-1002699763359,"messageId":763925}],"signature":"2|2|0|9|1|Banquier","finished":true},"1048":{"messages":[{"chatId":-1002699763359,"messageId":763926}],"signature":"2|2|8|9|1|Banquier","finished":true},"1049":{"messages":[{"chatId":-1002699763359,"messageId":763927}],"signature":"2|2|4|9|1|Banquier","finished":true},"1050":{"messages":[{"chatId":-1002699763359,"messageId":763928}],"signature":"2|2|9|0|1|Joueur","finished":true},"1051":{"messages":[{"chatId":-1002699763359,"messageId":763929}],"signature":"3|2|4|5|1|Banquier","finished":true},"1052":{"messages":[{"chatId":-1002699763359,"messageId":763930}],"signature":"3|2|6|7|1|Banquier","finished":true},"1053":{"messages":[{"chatId":-1002699763359,"messageId":763931}],"signature":"3|3|3|4|1|Banquier","finished":true},"1054":{"messages":[{"chatId":-1002699763359,"messageId":763932}],"signature":"3|2|1|4|1|Banquier","finished":true},"1055":{"messages":[{"chatId":-1002699763359,"messageId":763933}],"signature":"2|2|8|1|1|Joueur","finished":true},"1056":{"messages":[{"chatId":-1002699763359,"messageId":763934}],"signature":"3|3|8|1|1|Joueur","finished":true},"1057":{"messages":[{"chatId":-1002699763359,"messageId":763935}],"signature":"3|2|5|5|1|","finished":true},"1058":{"messages":[{"chatId":-1002699763359,"messageId":763936}],"signature":"2|2|0|8|1|Banquier","finished":true},"1059":{"messages":[{"chatId":-1002699763359,"messageId":763937}],"signature":"2|2|8|8|1|","finished":true},"1060":{"messages":[{"chatId":-1002699763359,"messageId":763938}],"signature":"3|3|1|5|1|Banquier","finished":true},"1061":{"messages":[{"chatId":-1002699763359,"messageId":763939}],"signature":"2|2|0|9|1|Banquier","finished":true},"1062":{"messages":[{"chatId":-1002699763359,"messageId":763940}],"signature":"3|2|1|7|1|Banquier","finished":true},"1063":{"messages":[{"chatId":-1002699763359,"messageId":763941}],"signature":"3|2|3|5|1|Banquier","finished":true},"1064":{"messages":[{"chatId":-1002699763359,"messageId":763942}],"signature":"3|2|6|6|1|","finished":true},"1065":{"messages":[{"chatId":-1002699763359,"messageId":763943}],"signature":"3|3|0|2|1|Banquier","finished":true},"1066":{"messages":[{"chatId":-1002699763359,"messageId":763944}],"signature":"3|3|0|1|1|Banquier","finished":true},"1067":{"messages":[{"chatId":-1002699763359,"messageId":763945}],"signature":"3|3|4|6|1|Banquier","finished":true},"1068":{"messages":[{"chatId":-1002699763359,"messageId":763946}],"signature":"2|2|0|9|1|Banquier","finished":true},"1069":{"messages":[{"chatId":-1002699763359,"messageId":763947}],"signature":"2|2|9|0|1|Joueur","finished":true},"1070":{"messages":[{"chatId":-1002699763359,"messageId":763948}],"signature":"2|2|9|2|1|Joueur","finished":true},"1071":{"messages":[{"chatId":-1002699763359,"messageId":763949}],"signature":"2|2|8|2|1|Joueur","finished":true},"1072":{"messages":[{"chatId":-1002699763359,"messageId":763950}],"signature":"3|3|4|5|1|Banquier","finished":true},"1073":{"messages":[{"chatId":-1002699763359,"messageId":763951}],"signature":"3|2|1|6|1|Banquier","finished":true},"1074":{"messages":[{"chatId":-1002699763359,"messageId":763952}],"signature":"3|3|6|2|1|Joueur","finished":true},"1075":{"messages":[{"chatId":-1002699763359,"messageId":763953}],"signature":"3|2|3|7|1|Banquier","finished":true},"1076":{"messages":[{"chatId":-1002699763359,"messageId":763954}],"signature":"2|2|8|9|1|Banquier","finished":true},"1077":{"messages":[{"chatId":-1002699763359,"messageId":763955}],"signature":"2|3|7|2|1|Joueur","finished":true},"1078":{"messages":[{"chatId":-1002699763359,"messageId":763956}],"signature":"2|2|5|9|1|Banquier","finished":true},"1079":{"messages":[{"chatId":-1002699763359,"messageId":763957}],"signature":"3|3|7|0|1|Joueur","finished":true},"1080":{"messages":[{"chatId":-1002699763359,"messageId":763958}],"signature":"3|2|0|7|1|Banquier","finished":true},"1081":{"messages":[{"chatId":-1002699763359,"messageId":763959}],"signature":"2|2|8|6|1|Joueur","finished":true},"1082":{"messages":[{"chatId":-1002699763359,"messageId":763960}],"signature":"3|2|4|5|1|Banquier","finished":true},"1083":{"messages":[{"chatId":-1002699763359,"messageId":763961}],"signature":"3|2|2|4|1|Banquier","finished":true},"1084":{"messages":[{"chatId":-1002699763359,"messageId":763962}],"signature":"2|2|5|8|1|Banquier","finished":true},"1085":{"messages":[{"chatId":-1002699763359,"messageId":763963}],"signature":"3|2|5|6|1|Banquier","finished":true},"1086":{"messages":[{"chatId":-1002699763359,"messageId":763964}],"signature":"3|3|3|0|1|Joueur","finished":true},"1087":{"messages":[{"chatId":-1002699763359,"messageId":763965}],"signature":"2|2|9|0|1|Joueur","finished":true},"1088":{"messages":[{"chatId":-1002699763359,"messageId":763966}],"signature":"3|3|4|6|1|Banquier","finished":true},"1089":{"messages":[{"chatId":-1002699763359,"messageId":763967}],"signature":"3|2|5|6|1|Banquier","finished":true},"1090":{"messages":[{"chatId":-1002699763359,"messageId":763968}],"signature":"3|2|0|5|1|Banquier","finished":true},"1091":{"messages":[{"chatId":-1002699763359,"messageId":763969}],"signature":"2|2|9|9|1|","finished":true},"1092":{"messages":[{"chatId":-1002699763359,"messageId":763970}],"signature":"3|3|1|3|1|Banquier","finished":true},"1093":{"messages":[{"chatId":-1002699763359,"messageId":763971}],"signature":"3|2|0|4|1|Banquier","finished":true},"1094":{"messages":[{"chatId":-1002699763359,"messageId":763972}],"signature":"2|2|6|9|1|Banquier","finished":true},"1095":{"messages":[{"chatId":-1002699763359,"messageId":763973}],"signature":"3|2|4|4|1|","finished":true},"1096":{"messages":[{"chatId":-1002699763359,"messageId":763974}],"signature":"2|2|3|8|1|Banquier","finished":true},"1097":{"messages":[{"chatId":-1002699763359,"messageId":763975}],"signature":"3|3|5|6|1|Banquier","finished":true},"1098":{"messages":[{"chatId":-1002699763359,"messageId":763976}],"signature":"3|3|5|8|1|Banquier","finished":true},"1099":{"messages":[{"chatId":-1002699763359,"messageId":763977}],"signature":"2|2|9|1|1|Joueur","finished":true},"1100":{"messages":[{"chatId":-1002699763359,"messageId":763978}],"signature":"3|3|4|3|1|Joueur","finished":true},"1101":{"messages":[{"chatId":-1002699763359,"messageId":763979}],"signature":"2|3|6|8|1|Banquier","finished":true},"1102":{"messages":[{"chatId":-1002699763359,"messageId":763980}],"signature":"2|3|7|6|1|Joueur","finished":true},"1103":{"messages":[{"chatId":-1002699763359,"messageId":763981}],"signature":"2|2|3|8|1|Banquier","finished":true},"1104":{"messages":[{"chatId":-1002699763359,"messageId":763982}],"signature":"3|3|7|3|1|Joueur","finished":true},"1105":{"messages":[{"chatId":-1002699763359,"messageId":763983}],"signature":"2|2|8|2|1|Joueur","finished":true},"1106":{"messages":[{"chatId":-1002699763359,"messageId":763984}],"signature":"2|2|7|6|1|Joueur","finished":true},"1107":{"messages":[{"chatId":-1002699763359,"messageId":763985}],"signature":"3|3|0|6|1|Banquier","finished":true},"1108":{"messages":[{"chatId":-1002699763359,"messageId":763986}],"signature":"2|3|7|4|1|Joueur","finished":true},"1109":{"messages":[{"chatId":-1002699763359,"messageId":763987}],"signature":"2|3|7|9|1|Banquier","finished":true},"1110":{"messages":[{"chatId":-1002699763359,"messageId":763988}],"signature":"3|2|5|7|1|Banquier","finished":true},"1111":{"messages":[{"chatId":-1002699763359,"messageId":763989}],"signature":"2|2|6|8|1|Banquier","finished":true},"1112":{"messages":[{"chatId":-1002699763359,"messageId":763990}],"signature":"2|2|9|7|1|Joueur","finished":true},"1113":{"messages":[{"chatId":-1002699763359,"messageId":763991}],"signature":"2|2|9|2|1|Joueur","finished":true},"1114":{"messages":[{"chatId":-1002699763359,"messageId":763992}],"signature":"3|2|7|6|1|Joueur","finished":true},"1115":{"messages":[{"chatId":-1002699763359,"messageId":763993}],"signature":"2|2|8|0|1|Joueur","finished":true},"1116":{"messages":[{"chatId":-1002699763359,"messageId":763994}],"signature":"2|2|6|8|1|Banquier","finished":true},"1117":{"messages":[{"chatId":-1002699763359,"messageId":763995}],"signature":"3|3|3|2|1|Joueur","finished":true},"1118":{"messages":[{"chatId":-1002699763359,"messageId":763996}],"signature":"2|2|7|6|1|Joueur","finished":true},"1119":{"messages":[{"chatId":-1002699763359,"messageId":763997}],"signature":"3|3|7|0|1|Joueur","finished":true},"1120":{"messages":[{"chatId":-1002699763359,"messageId":763998}],"signature":"3|3|6|0|1|Joueur","finished":true},"1121":{"messages":[{"chatId":-1002699763359,"messageId":763999}],"signature":"2|3|6|9|1|Banquier","finished":true},"1122":{"messages":[{"chatId":-1002699763359,"messageId":764000}],"signature":"2|2|9|6|1|Joueur","finished":true},"1123":{"messages":[{"chatId":-1002699763359,"messageId":764001}],"signature":"3|2|2|6|1|Banquier","finished":true},"1124":{"messages":[{"chatId":-1002699763359,"messageId":764002}],"signature":"3|2|5|7|1|Banquier","finished":true},"1125":{"messages":[{"chatId":-1002699763359,"messageId":764003}],"signature":"2|2|4|8|1|Banquier","finished":true},"1126":{"messages":[{"chatId":-1002699763359,"messageId":764004}],"signature":"2|3|7|7|1|","finished":true},"1127":{"messages":[{"chatId":-1002699763359,"messageId":764005}],"signature":"2|2|8|5|1|Joueur","finished":true},"1128":{"messages":[{"chatId":-1002699763359,"messageId":764006}],"signature":"3|3|1|7|1|Banquier","finished":true},"1129":{"messages":[{"chatId":-1002699763359,"messageId":764007}],"signature":"3|2|9|7|1|Joueur","finished":true},"1130":{"messages":[{"chatId":-1002699763359,"messageId":764008}],"signature":"3|2|0|6|1|Banquier","finished":true},"1131":{"messages":[{"chatId":-1002699763359,"messageId":764009}],"signature":"3|3|8|4|1|Joueur","finished":true},"1132":{"messages":[{"chatId":-1002699763359,"messageId":764010}],"signature":"2|2|4|9|1|Banquier","finished":true},"1133":{"messages":[{"chatId":-1002699763359,"messageId":764011}],"signature":"3|2|5|5|1|","finished":true},"1134":{"messages":[{"chatId":-1002699763359,"messageId":764012}],"signature":"3|3|7|9|1|Banquier","finished":true},"1135":{"messages":[{"chatId":-1002699763359,"messageId":764013}],"signature":"3|3|0|1|1|Banquier","finished":true},"1136":{"messages":[{"chatId":-1002699763359,"messageId":764014}],"signature":"3|3|6|4|1|Joueur","finished":true},"1137":{"messages":[{"chatId":-1002699763359,"messageId":764015}],"signature":"2|3|6|7|1|Banquier","finished":true},"1138":{"messages":[{"chatId":-1002699763359,"messageId":764016}],"signature":"2|3|6|5|1|Joueur","finished":true},"1139":{"messages":[{"chatId":-1002699763359,"messageId":764017}],"signature":"2|2|7|7|1|","finished":true},"1140":{"messages":[{"chatId":-1002699763359,"messageId":764018}],"signature":"2|2|8|3|1|Joueur","finished":true},"1141":{"messages":[{"chatId":-1002699763359,"messageId":764019}],"signature":"2|2|6|8|1|Banquier","finished":true},"1142":{"messages":[{"chatId":-1002699763359,"messageId":764020}],"signature":"2|2|4|8|1|Banquier","finished":true},"1143":{"messages":[{"chatId":-1002699763359,"messageId":764021}],"signature":"3|2|0|4|1|Banquier","finished":true},"1144":{"messages":[{"chatId":-1002699763359,"messageId":764022}],"signature":"2|2|8|6|1|Joueur","finished":true},"1145":{"messages":[{"chatId":-1002699763359,"messageId":764023}],"signature":"2|2|8|1|1|Joueur","finished":true},"1146":{"messages":[{"chatId":-1002699763359,"messageId":764024}],"signature":"3|2|5|4|1|Joueur","finished":true},"1147":{"messages":[{"chatId":-1002699763359,"messageId":764025}],"signature":"2|2|5|8|1|Banquier","finished":true},"1148":{"messages":[{"chatId":-1002699763359,"messageId":764026}],"signature":"3|2|8|5|1|Joueur","finished":true},"1149":{"messages":[{"chatId":-1002699763359,"messageId":764027}],"signature":"3|3|1|4|1|Banquier","finished":true},"1150":{"messages":[{"chatId":-1002699763359,"messageId":764028}],"signature":"2|2|0|8|1|Banquier","finished":true},"1151":{"messages":[{"chatId":-1002699763359,"messageId":764029}],"signature":"3|3|5|3|1|Joueur","finished":true},"1152":{"messages":[{"chatId":-1002699763359,"messageId":764030}],"signature":"2|3|6|6|1|","finished":true},"1153":{"messages":[{"chatId":-1002699763359,"messageId":764031}],"signature":"2|2|9|1|1|Joueur","finished":true},"1154":{"messages":[{"chatId":-1002699763359,"messageId":764032}],"signature":"3|3|0|4|1|Banquier","finished":true},"1155":{"messages":[{"chatId":-1002699763359,"messageId":764033}],"signature":"3|2|2|7|1|Banquier","finished":true},"1156":{"messages":[{"chatId":-1002699763359,"messageId":764034}],"signature":"3|3|8|9|1|Banquier","finished":true},"1157":{"messages":[{"chatId":-1002699763359,"messageId":764035}],"signature":"3|2|0|4|1|Banquier","finished":true},"1158":{"messages":[{"chatId":-1002699763359,"messageId":764036}],"signature":"2|2|8|5|1|Joueur","finished":true},"1159":{"messages":[{"chatId":-1002699763359,"messageId":764037}],"signature":"2|2|9|3|1|Joueur","finished":true},"1160":{"messages":[{"chatId":-1002699763359,"messageId":764038}],"signature":"2|2|4|9|1|Banquier","finished":true},"1161":{"messages":[{"chatId":-1002699763359,"messageId":764039}],"signature":"3|3|5|3|1|Joueur","finished":true},"1162":{"messages":[{"chatId":-1002699763359,"messageId":764040}],"signature":"3|3|2|5|1|Banquier","finished":true},"1163":{"messages":[{"chatId":-1002699763359,"messageId":764041}],"signature":"3|2|4|5|1|Banquier","finished":true},"1164":{"messages":[{"chatId":-1002699763359,"messageId":764042}],"signature":"2|2|2|8|1|Banquier","finished":true},"1165":{"messages":[{"chatId":-1002699763359,"messageId":764043}],"signature":"2|2|7|9|1|Banquier","finished":true},"1166":{"messages":[{"chatId":-1002699763359,"messageId":764044}],"signature":"2|2|6|8|1|Banquier","finished":true},"1167":{"messages":[{"chatId":-1002699763359,"messageId":764045}],"signature":"2|2|8|0|1|Joueur","finished":true},"1168":{"messages":[{"chatId":-1002699763359,"messageId":764046}],"signature":"3|2|4|7|1|Banquier","finished":true},"1169":{"messages":[{"chatId":-1002699763359,"messageId":764047}],"signature":"2|3|6|1|1|Joueur","finished":true},"1170":{"messages":[{"chatId":-1002699763359,"messageId":764048}],"signature":"2|2|9|1|1|Joueur","finished":true},"1171":{"messages":[{"chatId":-1002699763359,"messageId":764049}],"signature":"3|3|0|4|1|Banquier","finished":true},"1172":{"messages":[{"chatId":-1002699763359,"messageId":764050}],"signature":"2|2|8|6|1|Joueur","finished":true},"1173":{"messages":[{"chatId":-1002699763359,"messageId":764051}],"signature":"3|3|0|6|1|Banquier","finished":true},"1174":{"messages":[{"chatId":-1002699763359,"messageId":764052}],"signature":"3|3|3|9|1|Banquier","finished":true},"1175":{"messages":[{"chatId":-1002699763359,"messageId":764053}],"signature":"2|2|5|8|1|Banquier","finished":true},"1176":{"messages":[{"chatId":-1002699763359,"messageId":764054}],"signature":"2|3|6|9|1|Banquier","finished":true},"1177":{"messages":[{"chatId":-1002699763359,"messageId":764055}],"signature":"3|3|9|8|1|Joueur","finished":true},"1178":{"messages":[{"chatId":-1002699763359,"messageId":764056}],"signature":"2|2|0|8|1|Banquier","finished":true},"1179":{"messages":[{"chatId":-1002699763359,"messageId":764057}],"signature":"3|3|4|7|1|Banquier","finished":true},"1180":{"messages":[{"chatId":-1002699763359,"messageId":764058}],"signature":"3|2|2|4|1|Banquier","finished":true},"1181":{"messages":[{"chatId":-1002699763359,"messageId":764059}],"signature":"3|3|1|0|1|Joueur","finished":true},"1182":{"messages":[{"chatId":-1002699763359,"messageId":764060}],"signature":"2|2|8|4|1|Joueur","finished":true},"1183":{"messages":[{"chatId":-1002699763359,"messageId":764061}],"signature":"2|2|3|8|1|Banquier","finished":true},"1184":{"messages":[{"chatId":-1002699763359,"messageId":764062}],"signature":"2|2|0|9|1|Banquier","finished":true},"1185":{"messages":[{"chatId":-1002699763359,"messageId":764063}],"signature":"2|3|6|8|1|Banquier","finished":true},"1186":{"messages":[{"chatId":-1002699763359,"messageId":764064}],"signature":"3|3|1|1|1|","finished":true},"1187":{"messages":[{"chatId":-1002699763359,"messageId":764065}],"signature":"2|2|6|8|1|Banquier","finished":true},"1188":{"messages":[{"chatId":-1002699763359,"messageId":764066}],"signature":"3|3|5|0|1|Joueur","finished":true},"1189":{"messages":[{"chatId":-1002699763359,"messageId":764067}],"signature":"2|3|6|9|1|Banquier","finished":true},"1190":{"messages":[{"chatId":-1002699763359,"messageId":764068}],"signature":"3|3|4|8|1|Banquier","finished":true},"1191":{"messages":[{"chatId":-1002699763359,"messageId":764069}],"signature":"3|2|3|3|1|","finished":true},"1192":{"messages":[{"chatId":-1002699763359,"messageId":764070}],"signature":"2|2|7|8|1|Banquier","finished":true},"1193":{"messages":[{"chatId":-1002699763359,"messageId":764071}],"signature":"3|2|9|4|1|Joueur","finished":true},"1194":{"messages":[{"chatId":-1002699763359,"messageId":764072}],"signature":"3|3|4|5|1|Banquier","finished":true},"1195":{"messages":[{"chatId":-1002699763359,"messageId":764073}],"signature":"3|3|3|0|1|Joueur","finished":true},"1196":{"messages":[{"chatId":-1002699763359,"messageId":764074}],"signature":"2|2|6|9|1|Banquier","finished":true},"1197":{"messages":[{"chatId":-1002699763359,"messageId":764075}],"signature":"3|2|1|7|1|Banquier","finished":true},"1198":{"messages":[{"chatId":-1002699763359,"messageId":764076}],"signature":"2|2|6|6|1|","finished":true},"1199":{"messages":[{"chatId":-1002699763359,"messageId":764077}],"signature":"3|2|1|6|1|Banquier","finished":true},"1200":{"messages":[{"chatId":-1002699763359,"messageId":764078}],"signature":"2|2|4|9|1|Banquier","finished":true},"1201":{"messages":[{"chatId":-1002699763359,"messageId":764079}],"signature":"3|2|1|4|1|Banquier","finished":true},"1202":{"messages":[{"chatId":-1002699763359,"messageId":764080}],"signature":"2|2|0|9|1|Banquier","finished":true},"1203":{"messages":[{"chatId":-1002699763359,"messageId":764081}],"signature":"3|3|2|3|1|Banquier","finished":true},"1204":{"messages":[{"chatId":-1002699763359,"messageId":764082}],"signature":"3|2|2|6|1|Banquier","finished":true},"1205":{"messages":[{"chatId":-1002699763359,"messageId":764083}],"signature":"3|3|2|5|1|Banquier","finished":true},"1206":{"messages":[{"chatId":-1002699763359,"messageId":764084}],"signature":"2|3|6|0|1|Joueur","finished":true},"1207":{"messages":[{"chatId":-1002699763359,"messageId":764085}],"signature":"3|2|2|4|1|Banquier","finished":true},"1208":{"messages":[{"chatId":-1002699763359,"messageId":764086}],"signature":"2|2|9|2|1|Joueur","finished":true},"1209":{"messages":[{"chatId":-1002699763359,"messageId":764087}],"signature":"3|2|6|6|1|","finished":true},"1210":{"messages":[{"chatId":-1002699763359,"messageId":764088}],"signature":"2|3|6|3|1|Joueur","finished":true},"1211":{"messages":[{"chatId":-1002699763359,"messageId":764089}],"signature":"3|2|0|7|1|Banquier","finished":true},"1212":{"messages":[{"chatId":-1002699763359,"messageId":764090}],"signature":"2|2|8|5|1|Joueur","finished":true},"1213":{"messages":[{"chatId":-1002699763359,"messageId":764091}],"signature":"3|2|7|6|1|Joueur","finished":true},"1214":{"messages":[{"chatId":-1002699763359,"messa</v>
+        <v>{"config":{"enabled":true,"channels":[-1002699763359]},"tracked":{"179":{"messages":[{"chatId":-1002699763359,"messageId":764498}],"signature":"2|2|6|6|1|","finished":true},"180":{"messages":[{"chatId":-1002699763359,"messageId":764499}],"signature":"2|2|9|0|1|Joueur","finished":true},"181":{"messages":[{"chatId":-1002699763359,"messageId":764500}],"signature":"2|2|9|1|1|Joueur","finished":true},"182":{"messages":[{"chatId":-1002699763359,"messageId":764501}],"signature":"2|2|9|7|1|Joueur","finished":true},"183":{"messages":[{"chatId":-1002699763359,"messageId":764502}],"signature":"2|3|7|6|1|Joueur","finished":true},"184":{"messages":[{"chatId":-1002699763359,"messageId":764503}],"signature":"3|2|2|5|1|Banquier","finished":true},"185":{"messages":[{"chatId":-1002699763359,"messageId":764504}],"signature":"3|3|0|6|1|Banquier","finished":true},"186":{"messages":[{"chatId":-1002699763359,"messageId":764505}],"signature":"3|3|9|0|1|Joueur","finished":true},"187":{"messages":[{"chatId":-1002699763359,"messageId":764506}],"signature":"3|3|8|1|1|Joueur","finished":true},"188":{"messages":[{"chatId":-1002699763359,"messageId":764507}],"signature":"3|3|6|4|1|Joueur","finished":true},"189":{"messages":[{"chatId":-1002699763359,"messageId":764508}],"signature":"3|3|2|3|1|Banquier","finished":true},"190":{"messages":[{"chatId":-1002699763359,"messageId":764509}],"signature":"2|2|9|4|1|Joueur","finished":true},"191":{"messages":[{"chatId":-1002699763359,"messageId":764510}],"signature":"2|2|7|8|1|Banquier","finished":true},"192":{"messages":[{"chatId":-1002699763359,"messageId":764511}],"signature":"2|2|5|8|1|Banquier","finished":true},"193":{"messages":[{"chatId":-1002699763359,"messageId":764512}],"signature":"2|2|2|9|1|Banquier","finished":true},"194":{"messages":[{"chatId":-1002699763359,"messageId":764513}],"signature":"3|3|7|1|1|Joueur","finished":true},"195":{"messages":[{"chatId":-1002699763359,"messageId":764514}],"signature":"3|3|7|0|1|Joueur","finished":true},"196":{"messages":[{"chatId":-1002699763359,"messageId":764515}],"signature":"3|3|4|8|1|Banquier","finished":true},"197":{"messages":[{"chatId":-1002699763359,"messageId":764516}],"signature":"3|3|0|1|1|Banquier","finished":true},"198":{"messages":[{"chatId":-1002699763359,"messageId":764517}],"signature":"3|3|0|9|1|Banquier","finished":true},"199":{"messages":[{"chatId":-1002699763359,"messageId":764518}],"signature":"2|3|6|1|1|Joueur","finished":true},"200":{"messages":[{"chatId":-1002699763359,"messageId":764519}],"signature":"3|3|6|3|1|Joueur","finished":true},"201":{"messages":[{"chatId":-1002699763359,"messageId":764520}],"signature":"2|2|4|8|1|Banquier","finished":true},"202":{"messages":[{"chatId":-1002699763359,"messageId":764521}],"signature":"3|3|0|3|1|Banquier","finished":true},"203":{"messages":[{"chatId":-1002699763359,"messageId":764522}],"signature":"3|3|4|4|1|","finished":true},"204":{"messages":[{"chatId":-1002699763359,"messageId":764523}],"signature":"3|3|9|3|1|Joueur","finished":true},"205":{"messages":[{"chatId":-1002699763359,"messageId":764524}],"signature":"3|3|2|0|1|Joueur","finished":true},"206":{"messages":[{"chatId":-1002699763359,"messageId":764525}],"signature":"2|2|9|0|1|Joueur","finished":true},"207":{"messages":[{"chatId":-1002699763359,"messageId":764526}],"signature":"3|3|4|1|1|Joueur","finished":true},"208":{"messages":[{"chatId":-1002699763359,"messageId":764527}],"signature":"2|3|7|2|1|Joueur","finished":true},"209":{"messages":[{"chatId":-1002699763359,"messageId":764528}],"signature":"3|2|0|7|1|Banquier","finished":true},"210":{"messages":[{"chatId":-1002699763359,"messageId":764529}],"signature":"2|3|6|2|1|Joueur","finished":true},"211":{"messages":[{"chatId":-1002699763359,"messageId":764530}],"signature":"2|2|0|9|1|Banquier","finished":true},"212":{"messages":[{"chatId":-1002699763359,"messageId":764531}],"signature":"3|2|5|5|1|","finished":true},"213":{"messages":[{"chatId":-1002699763359,"messageId":764532}],"signature":"3|3|6|6|1|","finished":true},"214":{"messages":[{"chatId":-1002699763359,"messageId":764533}],"signature":"2|2|0|8|1|Banquier","finished":true},"215":{"messages":[{"chatId":-1002699763359,"messageId":764534}],"signature":"3|3|0|3|1|Banquier","finished":true},"216":{"messages":[{"chatId":-1002699763359,"messageId":764535}],"signature":"3|2|8|7|1|Joueur","finished":true},"217":{"messages":[{"chatId":-1002699763359,"messageId":764536}],"signature":"2|2|2|8|1|Banquier","finished":true},"218":{"messages":[{"chatId":-1002699763359,"messageId":764537}],"signature":"3|2|4|7|1|Banquier","finished":true},"219":{"messages":[{"chatId":-1002699763359,"messageId":764538}],"signature":"3|2|9|5|1|Joueur","finished":true},"220":{"messages":[{"chatId":-1002699763359,"messageId":764539}],"signature":"2|2|5|8|1|Banquier","finished":true},"221":{"messages":[{"chatId":-1002699763359,"messageId":764540}],"signature":"2|2|4|9|1|Banquier","finished":true},"222":{"messages":[{"chatId":-1002699763359,"messageId":764541}],"signature":"3|3|2|2|1|","finished":true},"223":{"messages":[{"chatId":-1002699763359,"messageId":764542}],"signature":"2|2|8|2|1|Joueur","finished":true},"224":{"messages":[{"chatId":-1002699763359,"messageId":764543}],"signature":"3|3|9|5|1|Joueur","finished":true},"225":{"messages":[{"chatId":-1002699763359,"messageId":764544}],"signature":"3|3|1|0|1|Joueur","finished":true},"226":{"messages":[{"chatId":-1002699763359,"messageId":764545}],"signature":"3|3|4|3|1|Joueur","finished":true},"227":{"messages":[{"chatId":-1002699763359,"messageId":764546}],"signature":"3|2|5|6|1|Banquier","finished":true},"228":{"messages":[{"chatId":-1002699763359,"messageId":764547}],"signature":"2|3|7|7|1|","finished":true},"229":{"messages":[{"chatId":-1002699763359,"messageId":764548}],"signature":"2|2|9|9|1|","finished":true},"230":{"messages":[{"chatId":-1002699763359,"messageId":764549}],"signature":"2|3|6|8|1|Banquier","finished":true},"231":{"messages":[{"chatId":-1002699763359,"messageId":764550}],"signature":"2|2|8|4|1|Joueur","finished":true},"232":{"messages":[{"chatId":-1002699763359,"messageId":764551}],"signature":"2|2|9|0|1|Joueur","finished":true},"233":{"messages":[{"chatId":-1002699763359,"messageId":764552}],"signature":"2|3|6|0|1|Joueur","finished":true},"234":{"messages":[{"chatId":-1002699763359,"messageId":764553}],"signature":"2|2|2|8|1|Banquier","finished":true},"235":{"messages":[{"chatId":-1002699763359,"messageId":764554}],"signature":"3|2|0|5|1|Banquier","finished":true},"236":{"messages":[{"chatId":-1002699763359,"messageId":764555}],"signature":"3|2|2|6|1|Banquier","finished":true},"237":{"messages":[{"chatId":-1002699763359,"messageId":764556}],"signature":"3|3|1|1|1|","finished":true},"238":{"messages":[{"chatId":-1002699763359,"messageId":764557}],"signature":"2|2|7|7|1|","finished":true},"239":{"messages":[{"chatId":-1002699763359,"messageId":764558}],"signature":"3|3|5|5|1|","finished":true},"240":{"messages":[{"chatId":-1002699763359,"messageId":764559}],"signature":"2|2|9|9|1|","finished":true},"241":{"messages":[{"chatId":-1002699763359,"messageId":764560}],"signature":"2|2|7|8|1|Banquier","finished":true},"242":{"messages":[{"chatId":-1002699763359,"messageId":764561}],"signature":"2|3|6|1|1|Joueur","finished":true},"243":{"messages":[{"chatId":-1002699763359,"messageId":764562}],"signature":"3|3|1|9|1|Banquier","finished":true},"244":{"messages":[{"chatId":-1002699763359,"messageId":764563}],"signature":"2|3|6|7|1|Banquier","finished":true},"245":{"messages":[{"chatId":-1002699763359,"messageId":764564}],"signature":"3|3|4|9|1|Banquier","finished":true},"246":{"messages":[{"chatId":-1002699763359,"messageId":764565}],"signature":"2|2|4|8|1|Banquier","finished":true},"247":{"messages":[{"chatId":-1002699763359,"messageId":764566}],"signature":"2|3|6|5|1|Joueur","finished":true},"248":{"messages":[{"chatId":-1002699763359,"messageId":764567}],"signature":"2|3|7|1|1|Joueur","finished":true},"249":{"messages":[{"chatId":-1002699763359,"messageId":764568}],"signature":"3|2|5|7|1|Banquier","finished":true},"250":{"messages":[{"chatId":-1002699763359,"messageId":764569}],"signature":"3|3|3|1|1|Joueur","finished":true},"251":{"messages":[{"chatId":-1002699763359,"messageId":764570}],"signature":"2|2|5|9|1|Banquier","finished":true},"252":{"messages":[{"chatId":-1002699763359,"messageId":764571}],"signature":"3|3|2|1|1|Joueur","finished":true},"253":{"messages":[{"chatId":-1002699763359,"messageId":764572}],"signature":"2|2|4|9|1|Banquier","finished":true},"254":{"messages":[{"chatId":-1002699763359,"messageId":764573}],"signature":"3|3|2|0|1|Joueur","finished":true},"255":{"messages":[{"chatId":-1002699763359,"messageId":764574}],"signature":"2|3|7|4|1|Joueur","finished":true},"256":{"messages":[{"chatId":-1002699763359,"messageId":764575}],"signature":"3|3|9|6|1|Joueur","finished":true},"257":{"messages":[{"chatId":-1002699763359,"messageId":764576}],"signature":"3|2|5|7|1|Banquier","finished":true},"258":{"messages":[{"chatId":-1002699763359,"messageId":764577}],"signature":"3|3|2|1|1|Joueur","finished":true},"259":{"messages":[{"chatId":-1002699763359,"messageId":764578}],"signature":"2|2|6|7|1|Banquier","finished":true},"260":{"messages":[{"chatId":-1002699763359,"messageId":764579}],"signature":"2|2|0|8|1|Banquier","finished":true},"261":{"messages":[{"chatId":-1002699763359,"messageId":764580}],"signature":"3|3|9|0|1|Joueur","finished":true},"262":{"messages":[{"chatId":-1002699763359,"messageId":764581}],"signature":"2|2|9|1|1|Joueur","finished":true},"263":{"messages":[{"chatId":-1002699763359,"messageId":764582}],"signature":"2|2|8|1|1|Joueur","finished":true},"264":{"messages":[{"chatId":-1002699763359,"messageId":764583}],"signature":"3|2|4|5|1|Banquier","finished":true},"265":{"messages":[{"chatId":-1002699763359,"messageId":764584}],"signature":"3|2|3|5|1|Banquier","finished":true},"266":{"messages":[{"chatId":-1002699763359,"messageId":764585}],"signature":"3|3|5|5|1|","finished":true},"267":{"messages":[{"chatId":-1002699763359,"messageId":764586}],"signature":"2|2|0|9|1|Banquier","finished":true},"268":{"messages":[{"chatId":-1002699763359,"messageId":764587}],"signature":"2|2|8|8|1|","finished":true},"269":{"messages":[{"chatId":-1002699763359,"messageId":764588}],"signature":"3|2|1|4|1|Banquier","finished":true},"270":{"messages":[{"chatId":-1002699763359,"messageId":764589}],"signature":"2|3|6|5|1|Joueur","finished":true},"271":{"messages":[{"chatId":-1002699763359,"messageId":764590}],"signature":"2|2|8|0|1|Joueur","finished":true},"272":{"messages":[{"chatId":-1002699763359,"messageId":764591}],"signature":"2|2|8|1|1|Joueur","finished":true},"273":{"messages":[{"chatId":-1002699763359,"messageId":764592}],"signature":"2|2|7|8|1|Banquier","finished":true},"274":{"messages":[{"chatId":-1002699763359,"messageId":764593}],"signature":"2|2|1|8|1|Banquier","finished":true},"275":{"messages":[{"chatId":-1002699763359,"messageId":764594}],"signature":"3|2|2|5|1|Banquier","finished":true},"276":{"messages":[{"chatId":-1002699763359,"messageId":764595}],"signature":"3|3|7|5|1|Joueur","finished":true},"277":{"messages":[{"chatId":-1002699763359,"messageId":764596}],"signature":"2|2|9|1|1|Joueur","finished":true},"278":{"messages":[{"chatId":-1002699763359,"messageId":764597}],"signature":"3|2|0|4|1|Banquier","finished":true},"279":{"messages":[{"chatId":-1002699763359,"messageId":764598}],"signature":"2|2|6|6|1|","finished":true},"280":{"messages":[{"chatId":-1002699763359,"messageId":764599}],"signature":"3|3|8|4|1|Joueur","finished":true},"281":{"messages":[{"chatId":-1002699763359,"messageId":764600}],"signature":"3|2|4|7|1|Banquier","finished":true},"282":{"messages":[{"chatId":-1002699763359,"messageId":764601}],"signature":"3|2|3|5|1|Banquier","finished":true},"283":{"messages":[{"chatId":-1002699763359,"messageId":764602}],"signature":"3|3|9|6|1|Joueur","finished":true},"284":{"messages":[{"chatId":-1002699763359,"messageId":764603}],"signature":"3|3|9|3|1|Joueur","finished":true},"285":{"messages":[{"chatId":-1002699763359,"messageId":764604}],"signature":"3|3|8|9|1|Banquier","finished":true},"286":{"messages":[{"chatId":-1002699763359,"messageId":764605}],"signature":"3|3|6|2|1|Joueur","finished":true},"287":{"messages":[{"chatId":-1002699763359,"messageId":764606}],"signature":"2|2|1|8|1|Banquier","finished":true},"288":{"messages":[{"chatId":-1002699763359,"messageId":764607}],"signature":"3|2|0|7|1|Banquier","finished":true},"289":{"messages":[{"chatId":-1002699763359,"messageId":764608}],"signature":"2|2|9|5|1|Joueur","finished":true},"290":{"messages":[{"chatId":-1002699763359,"messageId":764609}],"signature":"2|2|1|9|1|Banquier","finished":true},"291":{"messages":[{"chatId":-1002699763359,"messageId":764610}],"signature":"3|3|3|4|1|Banquier","finished":true},"292":{"messages":[{"chatId":-1002699763359,"messageId":764611}],"signature":"3|3|6|2|1|Joueur","finished":true},"293":{"messages":[{"chatId":-1002699763359,"messageId":764612}],"signature":"2|2|9|0|1|Joueur","finished":true},"294":{"messages":[{"chatId":-1002699763359,"messageId":764613}],"signature":"3|3|1|2|1|Banquier","finished":true},"295":{"messages":[{"chatId":-1002699763359,"messageId":764614}],"signature":"3|3|0|2|1|Banquier","finished":true},"296":{"messages":[{"chatId":-1002699763359,"messageId":764615}],"signature":"3|2|4|7|1|Banquier","finished":true},"297":{"messages":[{"chatId":-1002699763359,"messageId":764616}],"signature":"2|2|7|9|1|Banquier","finished":true},"298":{"messages":[{"chatId":-1002699763359,"messageId":764617}],"signature":"2|2|9|4|1|Joueur","finished":true},"299":{"messages":[{"chatId":-1002699763359,"messageId":764618}],"signature":"2|2|0|8|1|Banquier","finished":true},"300":{"messages":[{"chatId":-1002699763359,"messageId":764619}],"signature":"2|2|6|6|1|","finished":true},"301":{"messages":[{"chatId":-1002699763359,"messageId":764620}],"signature":"3|3|1|5|1|Banquier","finished":true},"302":{"messages":[{"chatId":-1002699763359,"messageId":764621}],"signature":"3|2|5|4|1|Joueur","finished":true},"303":{"messages":[{"chatId":-1002699763359,"messageId":764622}],"signature":"2|2|1|8|1|Banquier","finished":true},"304":{"messages":[{"chatId":-1002699763359,"messageId":764623}],"signature":"2|2|8|5|1|Joueur","finished":true},"305":{"messages":[{"chatId":-1002699763359,"messageId":764624}],"signature":"2|2|7|6|1|Joueur","finished":true},"306":{"messages":[{"chatId":-1002699763359,"messageId":764625}],"signature":"3|2|0|4|1|Banquier","finished":true},"307":{"messages":[{"chatId":-1002699763359,"messageId":764626}],"signature":"3|3|1|1|1|","finished":true},"308":{"messages":[{"chatId":-1002699763359,"messageId":764627}],"signature":"3|3|1|4|1|Banquier","finished":true},"309":{"messages":[{"chatId":-1002699763359,"messageId":764628}],"signature":"3|3|9|7|1|Joueur","finished":true},"310":{"messages":[{"chatId":-1002699763359,"messageId":764629}],"signature":"3|2|8|3|1|Joueur","finished":true},"311":{"messages":[{"chatId":-1002699763359,"messageId":764630}],"signature":"3|3|6|9|1|Banquier","finished":true},"312":{"messages":[{"chatId":-1002699763359,"messageId":764631}],"signature":"2|2|6|9|1|Banquier","finished":true},"313":{"messages":[{"chatId":-1002699763359,"messageId":764632}],"signature":"2|2|7|7|1|","finished":true},"314":{"messages":[{"chatId":-1002699763359,"messageId":764633}],"signature":"3|3|7|5|1|Joueur","finished":true},"315":{"messages":[{"chatId":-1002699763359,"messageId":764634}],"signature":"3|3|7|5|1|Joueur","finished":true},"316":{"messages":[{"chatId":-1002699763359,"messageId":764635}],"signature":"3|2|4|4|1|","finished":true},"317":{"messages":[{"chatId":-1002699763359,"messageId":764636}],"signature":"3|3|0|9|1|Banquier","finished":true},"318":{"messages":[{"chatId":-1002699763359,"messageId":764637}],"signature":"3|3|8|2|1|Joueur","finished":true},"319":{"messages":[{"chatId":-1002699763359,"messageId":764638}],"signature":"2|3|6|5|1|Joueur","finished":true},"320":{"messages":[{"chatId":-1002699763359,"messageId":764639}],"signature":"3|3|2|9|1|Banquier","finished":true},"321":{"messages":[{"chatId":-1002699763359,"messageId":764640}],"signature":"3|2|4|5|1|Banquier","finished":true},"322":{"messages":[{"chatId":-1002699763359,"messageId":764641}],"signature":"2|2|9|0|1|Joueur","finished":true},"323":{"messages":[{"chatId":-1002699763359,"messageId":764642}],"signature":"2|2|6|7|1|Banquier","finished":true},"324":{"messages":[{"chatId":-1002699763359,"messageId":764643}],"signature":"3|3|6|2|1|Joueur","finished":true},"325":{"messages":[{"chatId":-1002699763359,"messageId":764644}],"signature":"3|3|1|3|1|Banquier","finished":true},"326":{"messages":[{"chatId":-1002699763359,"messageId":764645}],"signature":"2|2|8|4|1|Joueur","finished":true},"327":{"messages":[{"chatId":-1002699763359,"messageId":764646}],"signature":"2|2|9|9|1|","finished":true},"328":{"messages":[{"chatId":-1002699763359,"messageId":764647}],"signature":"2|3|7|4|1|Joueur","finished":true},"329":{"messages":[{"chatId":-1002699763359,"messageId":764648}],"signature":"3|3|4|8|1|Banquier","finished":true},"330":{"messages":[{"chatId":-1002699763359,"messageId":764649}],"signature":"3|3|0|4|1|Banquier","finished":true},"331":{"messages":[{"chatId":-1002699763359,"messageId":764650}],"signature":"3|3|8|1|1|Joueur","finished":true},"332":{"messages":[{"chatId":-1002699763359,"messageId":764651}],"signature":"3|2|1|4|1|Banquier","finished":true},"333":{"messages":[{"chatId":-1002699763359,"messageId":764652}],"signature":"3|2|9|3|1|Joueur","finished":true},"334":{"messages":[{"chatId":-1002699763359,"messageId":764653}],"signature":"3|3|4|2|1|Joueur","finished":true},"335":{"messages":[{"chatId":-1002699763359,"messageId":764654}],"signature":"2|3|6|3|1|Joueur","finished":true},"336":{"messages":[{"chatId":-1002699763359,"messageId":764655}],"signature":"3|2|5|6|1|Banquier","finished":true},"337":{"messages":[{"chatId":-1002699763359,"messageId":764656}],"signature":"2|2|8|3|1|Joueur","finished":true},"338":{"messages":[{"chatId":-1002699763359,"messageId":764657}],"signature":"3|2|6|6|1|","finished":true},"339":{"messages":[{"chatId":-1002699763359,"messageId":764658}],"signature":"3|2|0|5|1|Banquier","finished":true},"340":{"messages":[{"chatId":-1002699763359,"messageId":764659}],"signature":"2|3|7|8|1|Banquier","finished":true},"341":{"messages":[{"chatId":-1002699763359,"messageId":764660}],"signature":"3|3|0|4|1|Banquier","finished":true},"342":{"messages":[{"chatId":-1002699763359,"messageId":764661}],"signature":"3|3|5|4|1|Joueur","finished":true},"343":{"messages":[{"chatId":-1002699763359,"messageId":764662}],"signature":"2|2|4|8|1|Banquier","finished":true},"344":{"messages":[{"chatId":-1002699763359,"messageId":764663}],"signature":"3|3|5|7|1|Banquier","finished":true},"345":{"messages":[{"chatId":-1002699763359,"messageId":764664}],"signature":"2|2|5|9|1|Banquier","finished":true},"346":{"messages":[{"chatId":-1002699763359,"messageId":764665}],"signature":"2|2|7|8|1|Banquier","finished":true},"347":{"messages":[{"chatId":-1002699763359,"messageId":764666}],"signature":"2|2|8|1|1|Joueur","finished":true},"348":{"messages":[{"chatId":-1002699763359,"messageId":764667}],"signature":"2|2|0|8|1|Banquier","finished":true},"349":{"messages":[{"chatId":-1002699763359,"messageId":764668}],"signature":"3|3|6|2|1|Joueur","finished":true},"350":{"messages":[{"chatId":-1002699763359,"messageId":764669}],"signature":"2|2|0|8|1|Banquier","finished":true},"351":{"messages":[{"chatId":-1002699763359,"messageId":764670}],"signature":"2|2|8|2|1|Joueur","finished":true},"352":{"messages":[{"chatId":-1002699763359,"messageId":764671}],"signature":"3|2|0|4|1|Banquier","finished":true},"353":{"messages":[{"chatId":-1002699763359,"messageId":764672}],"signature":"2|2|5|8|1|Banquier","finished":true},"354":{"messages":[{"chatId":-1002699763359,"messageId":764673}],"signature":"2|2|3|8|1|Banquier","finished":true},"355":{"messages":[{"chatId":-1002699763359,"messageId":764674}],"signature":"2|2|9|3|1|Joueur","finished":true},"356":{"messages":[{"chatId":-1002699763359,"messageId":764675}],"signature":"2|2|9|3|1|Joueur","finished":true},"357":{"messages":[{"chatId":-1002699763359,"messageId":764676}],"signature":"2|3|6|1|1|Joueur","finished":true},"358":{"messages":[{"chatId":-1002699763359,"messageId":764677}],"signature":"2|3|7|2|1|Joueur","finished":true},"359":{"messages":[{"chatId":-1002699763359,"messageId":764678}],"signature":"2|3|6|6|1|","finished":true},"360":{"messages":[{"chatId":-1002699763359,"messageId":764679}],"signature":"3|3|0|5|1|Banquier","finished":true},"361":{"messages":[{"chatId":-1002699763359,"messageId":764680}],"signature":"2|2|9|7|1|Joueur","finished":true},"362":{"messages":[{"chatId":-1002699763359,"messageId":764681}],"signature":"3|2|2|5|1|Banquier","finished":true},"363":{"messages":[{"chatId":-1002699763359,"messageId":764682}],"signature":"2|2|7|6|1|Joueur","finished":true},"364":{"messages":[{"chatId":-1002699763359,"messageId":764683}],"signature":"2|3|7|0|1|Joueur","finished":true},"365":{"messages":[{"chatId":-1002699763359,"messageId":764684}],"signature":"3|3|1|2|1|Banquier","finished":true},"366":{"messages":[{"chatId":-1002699763359,"messageId":764685}],"signature":"3|2|3|7|1|Banquier","finished":true},"367":{"messages":[{"chatId":-1002699763359,"messageId":764686}],"signature":"2|2|5|8|1|Banquier","finished":true},"368":{"messages":[{"chatId":-1002699763359,"messageId":764687}],"signature":"3|2|2|6|1|Banquier","finished":true},"369":{"messages":[{"chatId":-1002699763359,"messageId":764688}],"signature":"2|2|1|9|1|Banquier","finished":true},"370":{"messages":[{"chatId":-1002699763359,"messageId":764689}],"signature":"2|3|7|0|1|Joueur","finished":true},"371":{"messages":[{"chatId":-1002699763359,"messageId":764690}],"signature":"2|2|8|9|1|Banquier","finished":true},"372":{"messages":[{"chatId":-1002699763359,"messageId":764691}],"signature":"2|2|9|9|1|","finished":true},"373":{"messages":[{"chatId":-1002699763359,"messageId":764692}],"signature":"2|2|1|8|1|Banquier","finished":true},"374":{"messages":[{"chatId":-1002699763359,"messageId":764693}],"signature":"3|2|5|5|1|","finished":true},"375":{"messages":[{"chatId":-1002699763359,"messageId":764694}],"signature":"3|2|4|6|1|Banquier","finished":true},"376":{"messages":[{"chatId":-1002699763359,"messageId":764695}],"signature":"2|3|6|5|1|Joueur","finished":true},"377":{"messages":[{"chatId":-1002699763359,"messageId":764696}],"signature":"2|2|1|8|1|Banquier","finished":true},"378":{"messages":[{"chatId":-1002699763359,"messageId":764697}],"signature":"3|2|7|7|1|","finished":true},"379":{"messages":[{"chatId":-1002699763359,"messageId":764698}],"signature":"3|2|0|5|1|Banquier","finished":true},"380":{"messages":[{"chatId":-1002699763359,"messageId":764699}],"signature":"2|2|8|2|1|Joueur","finished":true},"381":{"messages":[{"chatId":-1002699763359,"messageId":764700}],"signature":"2|2|9|7|1|Joueur","finished":true},"382":{"messages":[{"chatId":-1002699763359,"messageId":764701}],"signature":"3|2|9|7|1|Joueur","finished":true},"383":{"messages":[{"chatId":-1002699763359,"messageId":764702}],"signature":"2|2|8|6|1|Joueur","finished":true},"384":{"messages":[{"chatId":-1002699763359,"messageId":764703}],"signature":"2|2|6|7|1|Banquier","finished":true},"385":{"messages":[{"chatId":-1002699763359,"messageId":764704}],"signature":"3|2|6|6|1|","finished":true},"386":{"messages":[{"chatId":-1002699763359,"messageId":764705}],"signature":"2|2|8|2|1|Joueur","finished":true},"387":{"messages":[{"chatId":-1002699763359,"messageId":764706}],"signature":"3|3|3|1|1|Joueur","finished":true},"388":{"messages":[{"chatId":-1002699763359,"messageId":764707}],"signature":"3|3|4|0|1|Joueur","finished":true},"389":{"messages":[{"chatId":-1002699763359,"messageId":764708}],"signature":"2|2|0|8|1|Banquier","finished":true},"390":{"messages":[{"chatId":-1002699763359,"messageId":764709}],"signature":"3|3|1|0|1|Joueur","finished":true},"391":{"messages":[{"chatId":-1002699763359,"messageId":764710}],"signature":"3|3|1|1|1|","finished":true},"392":{"messages":[{"chatId":-1002699763359,"messageId":764711}],"signature":"2|3|7|1|1|Joueur","finished":true},"393":{"messages":[{"chatId":-1002699763359,"messageId":764712}],"signature":"2|2|4|9|1|Banquier","finished":true},"394":{"messages":[{"chatId":-1002699763359,"messageId":764713}],"signature":"2|2|6|8|1|Banquier","finished":true},"395":{"messages":[{"chatId":-1002699763359,"messageId":764714}],"signature":"2|3|6|8|1|Banquier","finished":true},"396":{"messages":[{"chatId":-1002699763359,"messageId":764715}],"signature":"2|2|5|8|1|Banquier","finished":true},"397":{"messages":[{"chatId":-1002699763359,"messageId":764716}],"signature":"3|3|6|0|1|Joueur","finished":true},"398":{"messages":[{"chatId":-1002699763359,"messageId":764717}],"signature":"2|3|6|0|1|Joueur","finished":true},"399":{"messages":[{"chatId":-1002699763359,"messageId":764718}],"signature":"2|2|5|8|1|Banquier","finished":true},"400":{"messages":[{"chatId":-1002699763359,"messageId":764719}],"signature":"3|2|0|4|1|Banquier","finished":true},"401":{"messages":[{"chatId":-1002699763359,"messageId":764720}],"signature":"3|3|9|4|1|Joueur","finished":true},"402":{"messages":[{"chatId":-1002699763359,"messageId":764721}],"signature":"2|2|8|2|1|Joueur","finished":true},"403":{"messages":[{"chatId":-1002699763359,"messageId":764722}],"signature":"3|2|7|5|1|Joueur","finished":true},"404":{"messages":[{"chatId":-1002699763359,"messageId":764723}],"signature":"3|2|0|5|1|Banquier","finished":true},"405":{"messages":[{"chatId":-1002699763359,"messageId":764724}],"signature":"2|2|8|5|1|Joueur","finished":true},"406":{"messages":[{"chatId":-1002699763359,"messageId":764725}],"signature":"3|2|3|4|1|Banquier","finished":true},"407":{"messages":[{"chatId":-1002699763359,"messageId":764726}],"signature":"3|3|5|5|1|","finished":true},"408":{"messages":[{"chatId":-1002699763359,"messageId":764727}],"signature":"3|3|6|8|1|Banquier","finished":true},"409":{"messages":[{"chatId":-1002699763359,"messageId":764728}],"signature":"3|3|5|8|1|Banquier","finished":true},"410":{"messages":[{"chatId":-1002699763359,"messageId":764729}],"signature":"2|2|8|6|1|Joueur","finished":true},"411":{"messages":[{"chatId":-1002699763359,"messageId":764730}],"signature":"2|2|9|5|1|Joueur","finished":true},"412":{"messages":[{"chatId":-1002699763359,"messageId":764731}],"signature":"3|2|3|6|1|Banquier","finished":true},"413":{"messages":[{"chatId":-1002699763359,"messageId":764732}],"signature":"2|2|8|8|1|","finished":true},"414":{"messages":[{"chatId":-1002699763359,"messageId":764733}],"signature":"3|2|6|7|1|Banquier","finished":true},"415":{"messages":[{"chatId":-1002699763359,"messageId":764734}],"signature":"2|2|7|6|1|Joueur","finished":true},"416":{"messages":[{"chatId":-1002699763359,"messageId":764735}],"signature":"3|3|5|7|1|Banquier","finished":true},"417":{"messages":[{"chatId":-1002699763359,"messageId":764736}],"signature":"2|2|8|6|1|Joueur","finished":true},"418":{"messages":[{"chatId":-1002699763359,"messageId":764737}],"signature":"3|3|7|6|1|Joueur","finished":true},"419":{"messages":[{"chatId":-1002699763359,"messageId":764738}],"signature":"2|2|6|8|1|Banquier","finished":true},"420":{"messages":[{"chatId":-1002699763359,"messageId":764739}],"signature":"3|3|6|0|1|Joueur","finished":true},"421":{"messages":[{"chatId":-1002699763359,"messageId":764740}],"signature":"3|2|8|7|1|Joueur","finished":true},"422":{"messages":[{"chatId":-1002699763359,"messageId":764741}],"signature":"3|3|1|7|1|Banquier","finished":true},"423":{"messages":[{"chatId":-1002699763359,"messageId":764742}],"signature":"3|3|8|0|1|Joueur","finished":true},"424":{"messages":[{"chatId":-1002699763359,"messageId":764743}],"signature":"3|3|0|5|1|Banquier","finished":true},"425":{"messages":[{"chatId":-1002699763359,"messageId":764744}],"signature":"3|3|5|4|1|Joueur","finished":true},"426":{"messages":[{"chatId":-1002699763359,"messageId":764745}],"signature":"3|3|3|6|1|Banquier","finished":true},"427":{"messages":[{"chatId":-1002699763359,"messageId":764746}],"signature":"3|3|9|2|1|Joueur","finished":true},"428":{"messages":[{"chatId":-1002699763359,"messageId":764747}],"signature":"3|2|3|4|1|Banquier","finished":true},"429":{"messages":[{"chatId":-1002699763359,"messageId":764748}],"signature":"2|2|9|2|1|Joueur","finished":true},"430":{"messages":[{"chatId":-1002699763359,"messageId":764749}],"signature":"2|2|9|7|1|Joueur","finished":true},"431":{"messages":[{"chatId":-1002699763359,"messageId":764750}],"signature":"3|3|9|0|1|Joueur","finished":true},"432":{"messages":[{"chatId":-1002699763359,"messageId":764751}],"signature":"2|2|9|9|1|","finished":true},"433":{"messages":[{"chatId":-1002699763359,"messageId":764752}],"signature":"3|2|8|5|1|Joueur","finished":true},"434":{"messages":[{"chatId":-1002699763359,"messageId":764753}],"signature":"3|3|7|2|1|Joueur","finished":true},"435":{"messages":[{"chatId":-1002699763359,"messageId":764754}],"signature":"3|2|6|7|1|Banquier","finished":true},"436":{"messages":[{"chatId":-1002699763359,"messageId":764755}],"signature":"2|2|8|2|1|Joueur","finished":true},"437":{"messages":[{"chatId":-1002699763359,"messageId":764756}],"signature":"3|3|8|1|1|Joueur","finished":true},"438":{"messages":[{"chatId":-1002699763359,"messageId":764757}],"signature":"2|2|9|0|1|Joueur","finished":true},"439":{"messages":[{"chatId":-1002699763359,"messageId":764758}],"signature":"3|3|2|4|1|Banquier","finished":true},"440":{"messages":[{"chatId":-1002699763359,"messageId":764759}],"signature":"2|2|7|8|1|Banquier","finished":true},"441":{"messages":[{"chatId":-1002699763359,"messageId":764760}],"signature":"2|2|9|3|1|Joueur","finished":true},"442":{"messages":[{"chatId":-1002699763359,"messageId":764761}],"signature":"3|3|5|7|1|Banquier","finished":true},"443":{"messages":[{"chatId":-1002699763</v>
       </c>
     </row>
     <row r="10">
@@ -2465,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="str">
-        <v>geId":764092}],"signature":"2|2|9|6|1|Joueur","finished":true},"1215":{"messages":[{"chatId":-1002699763359,"messageId":764093}],"signature":"2|2|1|8|1|Banquier","finished":true},"1216":{"messages":[{"chatId":-1002699763359,"messageId":764094}],"signature":"3|3|5|3|1|Joueur","finished":true},"1217":{"messages":[{"chatId":-1002699763359,"messageId":764095}],"signature":"2|2|8|2|1|Joueur","finished":true},"1218":{"messages":[{"chatId":-1002699763359,"messageId":764096}],"signature":"3|3|1|0|1|Joueur","finished":true},"1219":{"messages":[{"chatId":-1002699763359,"messageId":764097}],"signature":"2|2|3|8|1|Banquier","finished":true},"1220":{"messages":[{"chatId":-1002699763359,"messageId":764098}],"signature":"2|2|5|9|1|Banquier","finished":true},"1221":{"messages":[{"chatId":-1002699763359,"messageId":764099}],"signature":"3|2|4|5|1|Banquier","finished":true},"1222":{"messages":[{"chatId":-1002699763359,"messageId":764100}],"signature":"2|3|6|0|1|Joueur","finished":true},"1223":{"messages":[{"chatId":-1002699763359,"messageId":764101}],"signature":"2|2|8|3|1|Joueur","finished":true},"1224":{"messages":[{"chatId":-1002699763359,"messageId":764102}],"signature":"2|2|9|1|1|Joueur","finished":true},"1225":{"messages":[{"chatId":-1002699763359,"messageId":764103}],"signature":"2|2|3|9|1|Banquier","finished":true},"1226":{"messages":[{"chatId":-1002699763359,"messageId":764104}],"signature":"3|3|9|4|1|Joueur","finished":true},"1227":{"messages":[{"chatId":-1002699763359,"messageId":764105}],"signature":"3|2|5|6|1|Banquier","finished":true},"1228":{"messages":[{"chatId":-1002699763359,"messageId":764106}],"signature":"3|3|9|6|1|Joueur","finished":true},"1229":{"messages":[{"chatId":-1002699763359,"messageId":764107}],"signature":"3|2|7|7|1|","finished":true},"1230":{"messages":[{"chatId":-1002699763359,"messageId":764108}],"signature":"2|2|1|9|1|Banquier","finished":true},"1231":{"messages":[{"chatId":-1002699763359,"messageId":764109}],"signature":"2|2|9|3|1|Joueur","finished":true},"1232":{"messages":[{"chatId":-1002699763359,"messageId":764110}],"signature":"2|2|8|1|1|Joueur","finished":true},"1233":{"messages":[{"chatId":-1002699763359,"messageId":764111}],"signature":"3|2|7|6|1|Joueur","finished":true},"1234":{"messages":[{"chatId":-1002699763359,"messageId":764112}],"signature":"2|3|7|2|1|Joueur","finished":true},"1235":{"messages":[{"chatId":-1002699763359,"messageId":764113}],"signature":"3|2|8|4|1|Joueur","finished":true},"1236":{"messages":[{"chatId":-1002699763359,"messageId":764114}],"signature":"3|2|0|4|1|Banquier","finished":true},"1237":{"messages":[{"chatId":-1002699763359,"messageId":764115}],"signature":"3|3|1|0|1|Joueur","finished":true},"1238":{"messages":[{"chatId":-1002699763359,"messageId":764116}],"signature":"3|3|4|2|1|Joueur","finished":true},"1239":{"messages":[{"chatId":-1002699763359,"messageId":764117}],"signature":"2|2|8|1|1|Joueur","finished":true},"1240":{"messages":[{"chatId":-1002699763359,"messageId":764118}],"signature":"3|2|1|6|1|Banquier","finished":true},"1241":{"messages":[{"chatId":-1002699763359,"messageId":764119}],"signature":"2|3|6|8|1|Banquier","finished":true},"1242":{"messages":[{"chatId":-1002699763359,"messageId":764120}],"signature":"2|2|9|5|1|Joueur","finished":true},"1243":{"messages":[{"chatId":-1002699763359,"messageId":764121}],"signature":"2|2|9|2|1|Joueur","finished":true},"1244":{"messages":[{"chatId":-1002699763359,"messageId":764122}],"signature":"2|2|0|9|1|Banquier","finished":true},"1245":{"messages":[{"chatId":-1002699763359,"messageId":764123}],"signature":"2|2|0|8|1|Banquier","finished":true},"1246":{"messages":[{"chatId":-1002699763359,"messageId":764124}],"signature":"3|3|3|0|1|Joueur","finished":true},"1247":{"messages":[{"chatId":-1002699763359,"messageId":764125}],"signature":"3|3|8|0|1|Joueur","finished":true},"1248":{"messages":[{"chatId":-1002699763359,"messageId":764126}],"signature":"2|3|7|7|1|","finished":true},"1249":{"messages":[{"chatId":-1002699763359,"messageId":764127}],"signature":"3|3|9|8|1|Joueur","finished":true},"1250":{"messages":[{"chatId":-1002699763359,"messageId":764128}],"signature":"2|2|8|9|1|Banquier","finished":true},"1251":{"messages":[{"chatId":-1002699763359,"messageId":764129}],"signature":"3|2|2|6|1|Banquier","finished":true},"1252":{"messages":[{"chatId":-1002699763359,"messageId":764130}],"signature":"3|2|4|6|1|Banquier","finished":true},"1253":{"messages":[{"chatId":-1002699763359,"messageId":764131}],"signature":"3|3|0|2|1|Banquier","finished":true},"1254":{"messages":[{"chatId":-1002699763359,"messageId":764132}],"signature":"2|2|9|3|1|Joueur","finished":true},"1255":{"messages":[{"chatId":-1002699763359,"messageId":764133}],"signature":"2|2|0|8|1|Banquier","finished":true},"1256":{"messages":[{"chatId":-1002699763359,"messageId":764134}],"signature":"3|2|0|7|1|Banquier","finished":true},"1257":{"messages":[{"chatId":-1002699763359,"messageId":764135}],"signature":"2|2|1|8|1|Banquier","finished":true},"1258":{"messages":[{"chatId":-1002699763359,"messageId":764136}],"signature":"3|3|0|1|1|Banquier","finished":true},"1259":{"messages":[{"chatId":-1002699763359,"messageId":764137}],"signature":"2|2|7|7|1|","finished":true},"1260":{"messages":[{"chatId":-1002699763359,"messageId":764138}],"signature":"3|3|2|3|1|Banquier","finished":true},"1261":{"messages":[{"chatId":-1002699763359,"messageId":764139}],"signature":"2|2|8|9|1|Banquier","finished":true},"1262":{"messages":[{"chatId":-1002699763359,"messageId":764140}],"signature":"2|2|9|4|1|Joueur","finished":true},"1263":{"messages":[{"chatId":-1002699763359,"messageId":764141}],"signature":"2|3|7|7|1|","finished":true},"1264":{"messages":[{"chatId":-1002699763359,"messageId":764142}],"signature":"2|2|8|3|1|Joueur","finished":true},"1265":{"messages":[{"chatId":-1002699763359,"messageId":764143}],"signature":"2|3|6|2|1|Joueur","finished":true},"1266":{"messages":[{"chatId":-1002699763359,"messageId":764144}],"signature":"2|2|9|3|1|Joueur","finished":true},"1267":{"messages":[{"chatId":-1002699763359,"messageId":764145}],"signature":"3|3|8|3|1|Joueur","finished":true},"1268":{"messages":[{"chatId":-1002699763359,"messageId":764146}],"signature":"3|3|3|0|1|Joueur","finished":true},"1269":{"messages":[{"chatId":-1002699763359,"messageId":764147}],"signature":"2|2|0|9|1|Banquier","finished":true},"1270":{"messages":[{"chatId":-1002699763359,"messageId":764148}],"signature":"3|3|0|3|1|Banquier","finished":true},"1271":{"messages":[{"chatId":-1002699763359,"messageId":764149}],"signature":"2|2|8|8|1|","finished":true},"1272":{"messages":[{"chatId":-1002699763359,"messageId":764150}],"signature":"2|2|4|9|1|Banquier","finished":true},"1273":{"messages":[{"chatId":-1002699763359,"messageId":764151}],"signature":"2|2|8|9|1|Banquier","finished":true},"1274":{"messages":[{"chatId":-1002699763359,"messageId":764152}],"signature":"3|3|1|1|1|","finished":true},"1275":{"messages":[{"chatId":-1002699763359,"messageId":764153}],"signature":"3|2|2|7|1|Banquier","finished":true},"1276":{"messages":[{"chatId":-1002699763359,"messageId":764154}],"signature":"2|2|1|9|1|Banquier","finished":true},"1277":{"messages":[{"chatId":-1002699763359,"messageId":764155}],"signature":"3|2|5|5|1|","finished":true},"1278":{"messages":[{"chatId":-1002699763359,"messageId":764156}],"signature":"2|2|9|4|1|Joueur","finished":true},"1279":{"messages":[{"chatId":-1002699763359,"messageId":764157}],"signature":"2|2|8|0|1|Joueur","finished":true},"1280":{"messages":[{"chatId":-1002699763359,"messageId":764158}],"signature":"3|3|5|4|1|Joueur","finished":true},"1281":{"messages":[{"chatId":-1002699763359,"messageId":764159}],"signature":"3|3|9|1|1|Joueur","finished":true},"1282":{"messages":[{"chatId":-1002699763359,"messageId":764160}],"signature":"2|2|3|8|1|Banquier","finished":true},"1283":{"messages":[{"chatId":-1002699763359,"messageId":764161}],"signature":"2|2|9|9|1|","finished":true},"1284":{"messages":[{"chatId":-1002699763359,"messageId":764162}],"signature":"2|3|7|4|1|Joueur","finished":true},"1285":{"messages":[{"chatId":-1002699763359,"messageId":764163}],"signature":"3|3|6|4|1|Joueur","finished":true},"1286":{"messages":[{"chatId":-1002699763359,"messageId":764164}],"signature":"3|2|8|7|1|Joueur","finished":true},"1287":{"messages":[{"chatId":-1002699763359,"messageId":764165}],"signature":"2|2|0|9|1|Banquier","finished":true},"1288":{"messages":[{"chatId":-1002699763359,"messageId":764166}],"signature":"2|2|9|1|1|Joueur","finished":true},"1289":{"messages":[{"chatId":-1002699763359,"messageId":764167}],"signature":"3|2|4|4|1|","finished":true},"1290":{"messages":[{"chatId":-1002699763359,"messageId":764168}],"signature":"2|3|6|3|1|Joueur","finished":true},"1291":{"messages":[{"chatId":-1002699763359,"messageId":764169}],"signature":"2|3|7|6|1|Joueur","finished":true},"1292":{"messages":[{"chatId":-1002699763359,"messageId":764170}],"signature":"3|3|3|1|1|Joueur","finished":true},"1293":{"messages":[{"chatId":-1002699763359,"messageId":764171}],"signature":"2|2|8|8|1|","finished":true},"1294":{"messages":[{"chatId":-1002699763359,"messageId":764172}],"signature":"2|2|8|3|1|Joueur","finished":true},"1295":{"messages":[{"chatId":-1002699763359,"messageId":764173}],"signature":"2|2|4|8|1|Banquier","finished":true},"1296":{"messages":[{"chatId":-1002699763359,"messageId":764174}],"signature":"2|3|6|2|1|Joueur","finished":true},"1297":{"messages":[{"chatId":-1002699763359,"messageId":764175}],"signature":"2|2|8|7|1|Joueur","finished":true},"1298":{"messages":[{"chatId":-1002699763359,"messageId":764176}],"signature":"2|2|1|9|1|Banquier","finished":true},"1299":{"messages":[{"chatId":-1002699763359,"messageId":764177}],"signature":"2|2|3|9|1|Banquier","finished":true},"1300":{"messages":[{"chatId":-1002699763359,"messageId":764178}],"signature":"2|3|7|8|1|Banquier","finished":true},"1301":{"messages":[{"chatId":-1002699763359,"messageId":764179}],"signature":"3|3|2|0|1|Joueur","finished":true},"1302":{"messages":[{"chatId":-1002699763359,"messageId":764180}],"signature":"2|2|0|8|1|Banquier","finished":true},"1303":{"messages":[{"chatId":-1002699763359,"messageId":764181}],"signature":"2|2|9|2|1|Joueur","finished":true},"1304":{"messages":[{"chatId":-1002699763359,"messageId":764182}],"signature":"3|3|7|4|1|Joueur","finished":true},"1305":{"messages":[{"chatId":-1002699763359,"messageId":764183}],"signature":"3|2|6|6|1|","finished":true},"1306":{"messages":[{"chatId":-1002699763359,"messageId":764184}],"signature":"2|2|2|8|1|Banquier","finished":true},"1307":{"messages":[{"chatId":-1002699763359,"messageId":764185}],"signature":"3|2|7|7|1|","finished":true},"1308":{"messages":[{"chatId":-1002699763359,"messageId":764186}],"signature":"3|2|3|5|1|Banquier","finished":true},"1309":{"messages":[{"chatId":-1002699763359,"messageId":764187}],"signature":"3|3|9|1|1|Joueur","finished":true},"1310":{"messages":[{"chatId":-1002699763359,"messageId":764188}],"signature":"2|2|8|4|1|Joueur","finished":true},"1311":{"messages":[{"chatId":-1002699763359,"messageId":764189}],"signature":"2|2|1|8|1|Banquier","finished":true},"1312":{"messages":[{"chatId":-1002699763359,"messageId":764190}],"signature":"2|2|9|4|1|Joueur","finished":true},"1313":{"messages":[{"chatId":-1002699763359,"messageId":764191}],"signature":"3|3|3|1|1|Joueur","finished":true},"1314":{"messages":[{"chatId":-1002699763359,"messageId":764192}],"signature":"2|2|3|9|1|Banquier","finished":true},"1315":{"messages":[{"chatId":-1002699763359,"messageId":764193}],"signature":"3|3|5|6|1|Banquier","finished":true},"1316":{"messages":[{"chatId":-1002699763359,"messageId":764194}],"signature":"3|3|9|3|1|Joueur","finished":true},"1317":{"messages":[{"chatId":-1002699763359,"messageId":764195}],"signature":"2|2|6|6|1|","finished":true},"1318":{"messages":[{"chatId":-1002699763359,"messageId":764196}],"signature":"3|2|8|7|1|Joueur","finished":true},"1319":{"messages":[{"chatId":-1002699763359,"messageId":764197}],"signature":"3|3|4|8|1|Banquier","finished":true},"1320":{"messages":[{"chatId":-1002699763359,"messageId":764198}],"signature":"3|3|5|7|1|Banquier","finished":true},"1321":{"messages":[{"chatId":-1002699763359,"messageId":764199}],"signature":"3|3|0|4|1|Banquier","finished":true},"1322":{"messages":[{"chatId":-1002699763359,"messageId":764200}],"signature":"2|2|7|8|1|Banquier","finished":true},"1323":{"messages":[{"chatId":-1002699763359,"messageId":764201}],"signature":"3|3|3|4|1|Banquier","finished":true},"1324":{"messages":[{"chatId":-1002699763359,"messageId":764202}],"signature":"2|2|8|0|1|Joueur","finished":true},"1325":{"messages":[{"chatId":-1002699763359,"messageId":764203}],"signature":"3|2|2|4|1|Banquier","finished":true},"1326":{"messages":[{"chatId":-1002699763359,"messageId":764204}],"signature":"3|3|0|3|1|Banquier","finished":true},"1327":{"messages":[{"chatId":-1002699763359,"messageId":764205}],"signature":"2|2|6|9|1|Banquier","finished":true},"1328":{"messages":[{"chatId":-1002699763359,"messageId":764206}],"signature":"2|2|6|9|1|Banquier","finished":true},"1329":{"messages":[{"chatId":-1002699763359,"messageId":764207}],"signature":"3|3|7|0|1|Joueur","finished":true},"1330":{"messages":[{"chatId":-1002699763359,"messageId":764208}],"signature":"3|3|8|1|1|Joueur","finished":true},"1331":{"messages":[{"chatId":-1002699763359,"messageId":764209}],"signature":"3|2|0|4|1|Banquier","finished":true},"1332":{"messages":[{"chatId":-1002699763359,"messageId":764210}],"signature":"2|3|7|0|1|Joueur","finished":true},"1333":{"messages":[{"chatId":-1002699763359,"messageId":764211}],"signature":"3|3|7|3|1|Joueur","finished":true},"1334":{"messages":[{"chatId":-1002699763359,"messageId":764212}],"signature":"2|2|6|9|1|Banquier","finished":true},"1335":{"messages":[{"chatId":-1002699763359,"messageId":764213}],"signature":"2|2|4|9|1|Banquier","finished":true},"1336":{"messages":[{"chatId":-1002699763359,"messageId":764214}],"signature":"3|3|7|0|1|Joueur","finished":true},"1337":{"messages":[{"chatId":-1002699763359,"messageId":764215}],"signature":"3|3|3|3|1|","finished":true},"1338":{"messages":[{"chatId":-1002699763359,"messageId":764216}],"signature":"2|2|4|8|1|Banquier","finished":true},"1339":{"messages":[{"chatId":-1002699763359,"messageId":764217}],"signature":"3|2|3|4|1|Banquier","finished":true},"1340":{"messages":[{"chatId":-1002699763359,"messageId":764218}],"signature":"3|2|0|7|1|Banquier","finished":true},"1341":{"messages":[{"chatId":-1002699763359,"messageId":764219}],"signature":"2|2|3|8|1|Banquier","finished":true},"1342":{"messages":[{"chatId":-1002699763359,"messageId":764220}],"signature":"2|3|6|3|1|Joueur","finished":true},"1343":{"messages":[{"chatId":-1002699763359,"messageId":764221}],"signature":"2|2|1|8|1|Banquier","finished":true},"1344":{"messages":[{"chatId":-1002699763359,"messageId":764222}],"signature":"2|3|6|0|1|Joueur","finished":true},"1345":{"messages":[{"chatId":-1002699763359,"messageId":764223}],"signature":"3|3|1|2|1|Banquier","finished":true},"1346":{"messages":[{"chatId":-1002699763359,"messageId":764224}],"signature":"2|3|6|2|1|Joueur","finished":true},"1347":{"messages":[{"chatId":-1002699763359,"messageId":764225}],"signature":"3|2|5|4|1|Joueur","finished":true},"1348":{"messages":[{"chatId":-1002699763359,"messageId":764226}],"signature":"3|2|5|4|1|Joueur","finished":true},"1349":{"messages":[{"chatId":-1002699763359,"messageId":764227}],"signature":"2|2|8|6|1|Joueur","finished":true},"1350":{"messages":[{"chatId":-1002699763359,"messageId":764228}],"signature":"3|3|4|6|1|Banquier","finished":true},"1351":{"messages":[{"chatId":-1002699763359,"messageId":764229}],"signature":"2|2|0|8|1|Banquier","finished":true},"1352":{"messages":[{"chatId":-1002699763359,"messageId":764230}],"signature":"2|2|1|9|1|Banquier","finished":true}},"sentCount":10031,"lastSentAt":1791153071152}</v>
+        <v>359,"messageId":764762}],"signature":"3|3|9|8|1|Joueur","finished":true},"444":{"messages":[{"chatId":-1002699763359,"messageId":764763}],"signature":"2|2|7|7|1|","finished":true},"445":{"messages":[{"chatId":-1002699763359,"messageId":764764}],"signature":"3|3|8|1|1|Joueur","finished":true},"446":{"messages":[{"chatId":-1002699763359,"messageId":764765}],"signature":"2|3|7|1|1|Joueur","finished":true},"447":{"messages":[{"chatId":-1002699763359,"messageId":764766}],"signature":"2|2|8|8|1|","finished":true},"448":{"messages":[{"chatId":-1002699763359,"messageId":764767}],"signature":"3|3|8|6|1|Joueur","finished":true},"449":{"messages":[{"chatId":-1002699763359,"messageId":764768}],"signature":"2|3|6|5|1|Joueur","finished":true},"450":{"messages":[{"chatId":-1002699763359,"messageId":764769}],"signature":"2|2|8|3|1|Joueur","finished":true},"451":{"messages":[{"chatId":-1002699763359,"messageId":764770}],"signature":"2|2|9|0|1|Joueur","finished":true},"452":{"messages":[{"chatId":-1002699763359,"messageId":764771}],"signature":"3|3|3|7|1|Banquier","finished":true},"453":{"messages":[{"chatId":-1002699763359,"messageId":764772}],"signature":"3|2|9|7|1|Joueur","finished":true},"454":{"messages":[{"chatId":-1002699763359,"messageId":764773}],"signature":"2|2|9|0|1|Joueur","finished":true},"455":{"messages":[{"chatId":-1002699763359,"messageId":764774}],"signature":"3|3|3|2|1|Joueur","finished":true},"456":{"messages":[{"chatId":-1002699763359,"messageId":764775}],"signature":"2|2|1|9|1|Banquier","finished":true},"457":{"messages":[{"chatId":-1002699763359,"messageId":764776}],"signature":"2|2|2|9|1|Banquier","finished":true},"458":{"messages":[{"chatId":-1002699763359,"messageId":764777}],"signature":"2|2|9|1|1|Joueur","finished":true},"459":{"messages":[{"chatId":-1002699763359,"messageId":764778}],"signature":"2|2|0|8|1|Banquier","finished":true},"460":{"messages":[{"chatId":-1002699763359,"messageId":764779}],"signature":"2|2|3|8|1|Banquier","finished":true},"461":{"messages":[{"chatId":-1002699763359,"messageId":764780}],"signature":"2|2|8|0|1|Joueur","finished":true},"462":{"messages":[{"chatId":-1002699763359,"messageId":764781}],"signature":"2|2|7|7|1|","finished":true},"463":{"messages":[{"chatId":-1002699763359,"messageId":764782}],"signature":"3|3|8|1|1|Joueur","finished":true},"464":{"messages":[{"chatId":-1002699763359,"messageId":764783}],"signature":"2|2|3|8|1|Banquier","finished":true},"465":{"messages":[{"chatId":-1002699763359,"messageId":764784}],"signature":"2|2|4|8|1|Banquier","finished":true},"466":{"messages":[{"chatId":-1002699763359,"messageId":764785}],"signature":"2|2|3|8|1|Banquier","finished":true},"467":{"messages":[{"chatId":-1002699763359,"messageId":764786}],"signature":"3|3|5|6|1|Banquier","finished":true},"468":{"messages":[{"chatId":-1002699763359,"messageId":764787}],"signature":"2|2|5|8|1|Banquier","finished":true},"469":{"messages":[{"chatId":-1002699763359,"messageId":764788}],"signature":"2|3|6|7|1|Banquier","finished":true},"470":{"messages":[{"chatId":-1002699763359,"messageId":764789}],"signature":"3|2|3|6|1|Banquier","finished":true},"471":{"messages":[{"chatId":-1002699763359,"messageId":764790}],"signature":"3|2|8|6|1|Joueur","finished":true},"472":{"messages":[{"chatId":-1002699763359,"messageId":764791}],"signature":"2|2|6|6|1|","finished":true},"473":{"messages":[{"chatId":-1002699763359,"messageId":764792}],"signature":"2|2|3|8|1|Banquier","finished":true},"474":{"messages":[{"chatId":-1002699763359,"messageId":764793}],"signature":"2|3|6|2|1|Joueur","finished":true},"475":{"messages":[{"chatId":-1002699763359,"messageId":764794}],"signature":"3|3|9|7|1|Joueur","finished":true},"476":{"messages":[{"chatId":-1002699763359,"messageId":764795}],"signature":"3|3|4|4|1|","finished":true},"477":{"messages":[{"chatId":-1002699763359,"messageId":764796}],"signature":"2|2|9|4|1|Joueur","finished":true},"478":{"messages":[{"chatId":-1002699763359,"messageId":764797}],"signature":"3|2|1|7|1|Banquier","finished":true},"479":{"messages":[{"chatId":-1002699763359,"messageId":764798}],"signature":"2|3|6|3|1|Joueur","finished":true},"480":{"messages":[{"chatId":-1002699763359,"messageId":764799}],"signature":"3|3|2|3|1|Banquier","finished":true},"481":{"messages":[{"chatId":-1002699763359,"messageId":764800}],"signature":"2|2|1|8|1|Banquier","finished":true},"482":{"messages":[{"chatId":-1002699763359,"messageId":764801}],"signature":"2|2|1|9|1|Banquier","finished":true},"483":{"messages":[{"chatId":-1002699763359,"messageId":764802}],"signature":"3|2|8|4|1|Joueur","finished":true},"484":{"messages":[{"chatId":-1002699763359,"messageId":764803}],"signature":"3|3|6|4|1|Joueur","finished":true},"485":{"messages":[{"chatId":-1002699763359,"messageId":764804}],"signature":"2|2|9|2|1|Joueur","finished":true},"486":{"messages":[{"chatId":-1002699763359,"messageId":764805}],"signature":"3|3|2|0|1|Joueur","finished":true},"487":{"messages":[{"chatId":-1002699763359,"messageId":764806}],"signature":"3|3|4|3|1|Joueur","finished":true},"488":{"messages":[{"chatId":-1002699763359,"messageId":764807}],"signature":"2|2|9|2|1|Joueur","finished":true},"489":{"messages":[{"chatId":-1002699763359,"messageId":764808}],"signature":"2|2|8|2|1|Joueur","finished":true},"490":{"messages":[{"chatId":-1002699763359,"messageId":764809}],"signature":"3|3|0|1|1|Banquier","finished":true},"491":{"messages":[{"chatId":-1002699763359,"messageId":764810}],"signature":"2|3|7|5|1|Joueur","finished":true},"492":{"messages":[{"chatId":-1002699763359,"messageId":764811}],"signature":"2|3|6|5|1|Joueur","finished":true},"493":{"messages":[{"chatId":-1002699763359,"messageId":764812}],"signature":"2|2|5|8|1|Banquier","finished":true},"494":{"messages":[{"chatId":-1002699763359,"messageId":764813}],"signature":"2|3|6|0|1|Joueur","finished":true},"495":{"messages":[{"chatId":-1002699763359,"messageId":764814}],"signature":"2|2|6|7|1|Banquier","finished":true},"496":{"messages":[{"chatId":-1002699763359,"messageId":764815}],"signature":"2|2|0|9|1|Banquier","finished":true},"497":{"messages":[{"chatId":-1002699763359,"messageId":764816}],"signature":"3|3|0|0|1|","finished":true},"498":{"messages":[{"chatId":-1002699763359,"messageId":764817}],"signature":"3|3|9|5|1|Joueur","finished":true},"499":{"messages":[{"chatId":-1002699763359,"messageId":764818}],"signature":"2|3|6|8|1|Banquier","finished":true},"500":{"messages":[{"chatId":-1002699763359,"messageId":764819}],"signature":"2|2|9|9|1|","finished":true},"501":{"messages":[{"chatId":-1002699763359,"messageId":764820}],"signature":"3|3|0|1|1|Banquier","finished":true},"502":{"messages":[{"chatId":-1002699763359,"messageId":764821}],"signature":"2|3|7|3|1|Joueur","finished":true},"503":{"messages":[{"chatId":-1002699763359,"messageId":764822}],"signature":"3|2|6|6|1|","finished":true},"504":{"messages":[{"chatId":-1002699763359,"messageId":764823}],"signature":"3|2|2|6|1|Banquier","finished":true},"505":{"messages":[{"chatId":-1002699763359,"messageId":764824}],"signature":"2|3|6|8|1|Banquier","finished":true},"506":{"messages":[{"chatId":-1002699763359,"messageId":764825}],"signature":"2|2|0|8|1|Banquier","finished":true},"507":{"messages":[{"chatId":-1002699763359,"messageId":764826}],"signature":"3|3|2|7|1|Banquier","finished":true},"508":{"messages":[{"chatId":-1002699763359,"messageId":764827}],"signature":"3|3|2|0|1|Joueur","finished":true},"509":{"messages":[{"chatId":-1002699763359,"messageId":764828}],"signature":"3|3|1|8|1|Banquier","finished":true},"510":{"messages":[{"chatId":-1002699763359,"messageId":764829}],"signature":"2|2|2|8|1|Banquier","finished":true},"511":{"messages":[{"chatId":-1002699763359,"messageId":764830}],"signature":"2|2|9|0|1|Joueur","finished":true},"512":{"messages":[{"chatId":-1002699763359,"messageId":764831}],"signature":"2|2|0|9|1|Banquier","finished":true},"513":{"messages":[{"chatId":-1002699763359,"messageId":764832}],"signature":"2|3|6|0|1|Joueur","finished":true},"514":{"messages":[{"chatId":-1002699763359,"messageId":764833}],"signature":"2|3|6|5|1|Joueur","finished":true},"515":{"messages":[{"chatId":-1002699763359,"messageId":764834}],"signature":"2|2|7|9|1|Banquier","finished":true},"516":{"messages":[{"chatId":-1002699763359,"messageId":764835}],"signature":"2|2|0|8|1|Banquier","finished":true},"517":{"messages":[{"chatId":-1002699763359,"messageId":764836}],"signature":"2|2|5|9|1|Banquier","finished":true},"518":{"messages":[{"chatId":-1002699763359,"messageId":764837}],"signature":"2|2|9|7|1|Joueur","finished":true},"519":{"messages":[{"chatId":-1002699763359,"messageId":764838}],"signature":"3|2|6|7|1|Banquier","finished":true},"520":{"messages":[{"chatId":-1002699763359,"messageId":764839}],"signature":"2|3|6|3|1|Joueur","finished":true},"521":{"messages":[{"chatId":-1002699763359,"messageId":764840}],"signature":"2|2|9|9|1|","finished":true},"522":{"messages":[{"chatId":-1002699763359,"messageId":764841}],"signature":"3|3|8|3|1|Joueur","finished":true},"523":{"messages":[{"chatId":-1002699763359,"messageId":764842}],"signature":"2|2|9|7|1|Joueur","finished":true},"524":{"messages":[{"chatId":-1002699763359,"messageId":764843}],"signature":"3|3|1|7|1|Banquier","finished":true},"525":{"messages":[{"chatId":-1002699763359,"messageId":764844}],"signature":"2|3|7|9|1|Banquier","finished":true},"526":{"messages":[{"chatId":-1002699763359,"messageId":764845}],"signature":"3|2|9|5|1|Joueur","finished":true},"527":{"messages":[{"chatId":-1002699763359,"messageId":764846}],"signature":"3|3|8|9|1|Banquier","finished":true},"528":{"messages":[{"chatId":-1002699763359,"messageId":764847}],"signature":"2|2|8|6|1|Joueur","finished":true},"529":{"messages":[{"chatId":-1002699763359,"messageId":764848}],"signature":"2|2|8|7|1|Joueur","finished":true},"530":{"messages":[{"chatId":-1002699763359,"messageId":764849}],"signature":"3|3|0|1|1|Banquier","finished":true},"531":{"messages":[{"chatId":-1002699763359,"messageId":764850}],"signature":"3|3|7|7|1|","finished":true},"532":{"messages":[{"chatId":-1002699763359,"messageId":764851}],"signature":"2|2|8|9|1|Banquier","finished":true},"533":{"messages":[{"chatId":-1002699763359,"messageId":764852}],"signature":"3|3|1|7|1|Banquier","finished":true},"534":{"messages":[{"chatId":-1002699763359,"messageId":764853}],"signature":"2|2|8|0|1|Joueur","finished":true},"535":{"messages":[{"chatId":-1002699763359,"messageId":764854}],"signature":"2|2|0|8|1|Banquier","finished":true},"536":{"messages":[{"chatId":-1002699763359,"messageId":764855}],"signature":"2|2|8|9|1|Banquier","finished":true},"537":{"messages":[{"chatId":-1002699763359,"messageId":764856}],"signature":"3|3|5|3|1|Joueur","finished":true},"538":{"messages":[{"chatId":-1002699763359,"messageId":764857}],"signature":"3|2|2|7|1|Banquier","finished":true},"539":{"messages":[{"chatId":-1002699763359,"messageId":764858}],"signature":"3|3|1|1|1|","finished":true},"540":{"messages":[{"chatId":-1002699763359,"messageId":764859}],"signature":"2|3|6|1|1|Joueur","finished":true},"541":{"messages":[{"chatId":-1002699763359,"messageId":764860}],"signature":"3|3|2|0|1|Joueur","finished":true},"542":{"messages":[{"chatId":-1002699763359,"messageId":764861}],"signature":"2|2|9|3|1|Joueur","finished":true},"543":{"messages":[{"chatId":-1002699763359,"messageId":764862}],"signature":"2|2|8|1|1|Joueur","finished":true},"544":{"messages":[{"chatId":-1002699763359,"messageId":764863}],"signature":"2|2|7|7|1|","finished":true},"545":{"messages":[{"chatId":-1002699763359,"messageId":764864}],"signature":"2|3|7|9|1|Banquier","finished":true},"546":{"messages":[{"chatId":-1002699763359,"messageId":764865}],"signature":"3|2|4|6|1|Banquier","finished":true},"547":{"messages":[{"chatId":-1002699763359,"messageId":764866}],"signature":"3|3|7|1|1|Joueur","finished":true},"548":{"messages":[{"chatId":-1002699763359,"messageId":764867}],"signature":"2|2|8|9|1|Banquier","finished":true},"549":{"messages":[{"chatId":-1002699763359,"messageId":764868}],"signature":"3|3|2|5|1|Banquier","finished":true},"550":{"messages":[{"chatId":-1002699763359,"messageId":764869}],"signature":"3|3|1|9|1|Banquier","finished":true},"551":{"messages":[{"chatId":-1002699763359,"messageId":764870}],"signature":"2|2|2|8|1|Banquier","finished":true},"552":{"messages":[{"chatId":-1002699763359,"messageId":764871}],"signature":"3|3|8|7|1|Joueur","finished":true},"553":{"messages":[{"chatId":-1002699763359,"messageId":764872}],"signature":"3|3|8|8|1|","finished":true},"554":{"messages":[{"chatId":-1002699763359,"messageId":764873}],"signature":"2|3|7|7|1|","finished":true},"555":{"messages":[{"chatId":-1002699763359,"messageId":764874}],"signature":"2|2|0|8|1|Banquier","finished":true},"556":{"messages":[{"chatId":-1002699763359,"messageId":764875}],"signature":"2|3|7|4|1|Joueur","finished":true},"557":{"messages":[{"chatId":-1002699763359,"messageId":764876}],"signature":"2|3|6|2|1|Joueur","finished":true},"558":{"messages":[{"chatId":-1002699763359,"messageId":764877}],"signature":"2|2|0|9|1|Banquier","finished":true},"559":{"messages":[{"chatId":-1002699763359,"messageId":764878}],"signature":"3|3|4|2|1|Joueur","finished":true},"560":{"messages":[{"chatId":-1002699763359,"messageId":764879}],"signature":"3|2|4|6|1|Banquier","finished":true},"561":{"messages":[{"chatId":-1002699763359,"messageId":764880}],"signature":"3|3|5|2|1|Joueur","finished":true},"562":{"messages":[{"chatId":-1002699763359,"messageId":764881}],"signature":"2|3|6|8|1|Banquier","finished":true},"563":{"messages":[{"chatId":-1002699763359,"messageId":764882}],"signature":"3|3|0|3|1|Banquier","finished":true},"564":{"messages":[{"chatId":-1002699763359,"messageId":764883}],"signature":"3|3|7|0|1|Joueur","finished":true},"565":{"messages":[{"chatId":-1002699763359,"messageId":764884}],"signature":"2|2|7|7|1|","finished":true},"566":{"messages":[{"chatId":-1002699763359,"messageId":764885}],"signature":"3|3|2|0|1|Joueur","finished":true},"567":{"messages":[{"chatId":-1002699763359,"messageId":764886}],"signature":"2|3|6|7|1|Banquier","finished":true},"568":{"messages":[{"chatId":-1002699763359,"messageId":764887}],"signature":"3|3|8|0|1|Joueur","finished":true},"569":{"messages":[{"chatId":-1002699763359,"messageId":764888}],"signature":"2|2|8|6|1|Joueur","finished":true},"570":{"messages":[{"chatId":-1002699763359,"messageId":764889}],"signature":"2|3|7|7|1|","finished":true},"571":{"messages":[{"chatId":-1002699763359,"messageId":764890}],"signature":"2|2|1|9|1|Banquier","finished":true},"572":{"messages":[{"chatId":-1002699763359,"messageId":764891}],"signature":"3|3|7|6|1|Joueur","finished":true},"573":{"messages":[{"chatId":-1002699763359,"messageId":764892}],"signature":"3|3|7|9|1|Banquier","finished":true},"574":{"messages":[{"chatId":-1002699763359,"messageId":764893}],"signature":"2|3|6|9|1|Banquier","finished":true},"575":{"messages":[{"chatId":-1002699763359,"messageId":764894}],"signature":"2|2|5|9|1|Banquier","finished":true},"576":{"messages":[{"chatId":-1002699763359,"messageId":764895}],"signature":"3|2|4|4|1|","finished":true},"577":{"messages":[{"chatId":-1002699763359,"messageId":764896}],"signature":"2|2|8|3|1|Joueur","finished":true},"578":{"messages":[{"chatId":-1002699763359,"messageId":764897}],"signature":"2|2|9|6|1|Joueur","finished":true}},"sentCount":10623,"lastSentAt":1791193027640}</v>
       </c>
     </row>
     <row r="11">
@@ -2476,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"maxR":3,"predictionCount":1,"trigger":"both","blockSize":30,"categoriesOn":{"3/2":false,"3/3":false,"2/2":true},"categoryChannels":{"3/2":[],"3/3":[],"2/2":[-1004387601010]},"categorySiteChannels":{"3/2":null,"3/3":null,"2/2":null}},"history":[{"start":1321,"end":1350,"counts":{"3/2":6,"3/3":10,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791153010423},{"start":1291,"end":1320,"counts":{"3/2":4,"3/3":9,"2/2":14},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791151200584},{"start":1261,"end":1290,"counts":{"3/2":4,"3/3":7,"2/2":15},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791149379988},{"start":1231,"end":1260,"counts":{"3/2":7,"3/3":8,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791147599688},{"start":1201,"end":1230,"counts":{"3/2":9,"3/3":6,"2/2":12},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791145749838},{"start":1171,"end":1200,"counts":{"3/2":5,"3/3":11,"2/2":11},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791143944390},{"start":1141,"end":1170,"counts":{"3/2":7,"3/3":6,"2/2":15},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791142154372},{"start":1111,"end":1140,"counts":{"3/2":6,"3/3":8,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791140348685},{"start":1081,"end":1110,"counts":{"3/2":8,"3/3":8,"2/2":10},"predicted":false,"signal":null,"selected":false,"targets":[],"closedAt":1791138573389},{"start":1051,"end":1080,"counts":{"3/2":10,"3/3":9,"2/2":10},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791136773190},{"start":1021,"end":1050,"counts":{"3/2":7,"3/3":8,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791134953432},{"start":991,"end":1020,"counts":{"3/2":10,"3/3":10,"2/2":7},"predicted":true,"signal":"2/2","selected":true,"targets":[1025],"closedAt":1791133207783},{"start":961,"end":990,"counts":{"3/2":5,"3/3":7,"2/2":15},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791131382486},{"start":931,"end":960,"counts":{"3/2":4,"3/3":12,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791129552184},{"start":901,"end":930,"counts":{"3/2":9,"3/3":6,"2/2":12},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791127776954},{"start":871,"end":900,"counts":{"3/2":7,"3/3":7,"2/2":12},"predicted":false,"signal":null,"selected":false,"targets":[],"closedAt":1791126007066},{"start":841,"end":870,"counts":{"3/2":5,"3/3":11,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791124206986},{"start":811,"end":840,"counts":{"3/2":7,"3/3":9,"2/2":13},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791122347596},{"start":781,"end":810,"counts":{"3/2":5,"3/3":11,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791120552684},{"start":751,"end":780,"counts":{"3/2":2,"3/3":14,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791118801539},{"start":721,"end":750,"counts":{"3/2":3,"3/3":10,"2/2":14},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791116981886},{"start":691,"end":720,"counts":{"3/2":2,"3/3":14,"2/2":11},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791115146385},{"start":661,"end":690,"counts":{"3/2":7,"3/3":8,"2/2":9},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791113375985},{"start":631,"end":660,"counts":{"3/2":4,"3/3":8,"2/2":14},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791111606047},{"start":601,"end":630,"counts":{"3/2":7,"3/3":6,"2/2":13},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791109806486},{"start":571,"end":600,"counts":{"3/2":5,"3/3":15,"2/2":8},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791108005189},{"start":541,"end":570,"counts":{"3/2":8,"3/3":11,"2/2":8},"predicted":true,"signal":"2/2","selected":true,"targets":[575],"closedAt":1791106174731},{"start":511,"end":540,"counts":{"3/2":6,"3/3":8,"2/2":13},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791104404476},{"start":481,"end":510,"counts":{"3/2":1,"3/3":12,"2/2":13},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791102544592},{"start":451,"end":480,"counts":{"3/2":4,"3/3":10,"2/2":13},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791100774515},{"start":421,"end":450,"counts":{"3/2":8,"3/3":9,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791098949592},{"start":391,"end":420,"counts":{"3/2":8,"3/3":3,"2/2":13},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791097149075},{"start":361,"end":390,"counts":{"3/2":4,"3/3":12,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791095348186},{"start":331,"end":360,"counts":{"3/2":8,"3/3":7,"2/2":13},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791093572905},{"start":301,"end":330,"counts":{"3/2":7,"3/3":8,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791091772954},{"start":271,"end":300,"counts":{"3/2":5,"3/3":15,"2/2":8},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791090007686},{"start":241,"end":270,"counts":{"3/2":3,"3/3":14,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791088147948},{"start":211,"end":240,"counts":{"3/2":2,"3/3":11,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791086347345},{"start":181,"end":210,"counts":{"3/2":7,"3/3":14,"2/2":6},"predicted":true,"signal":"2/2","selected":true,"targets":[215],"closedAt":1791084606913},{"start":151,"end":180,"counts":{"3/2":10,"3/3":8,"2/2":10},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791082752168},{"start":121,"end":150,"counts":{"3/2":11,"3/3":9,"2/2":7},"predicted":true,"signal":"2/2","selected":true,"targets":[155],"closedAt":1791081001542},{"start":91,"end":120,"counts":{"3/2":8,"3/3":7,"2/2":10},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791079171582},{"start":61,"end":90,"counts":{"3/2":7,"3/3":6,"2/2":13},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791077346467},{"start":31,"end":60,"counts":{"3/2":6,"3/3":12,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791075606374},{"start":1,"end":30,"counts":{"3/2":4,"3/3":10,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791073746330},{"start":1141,"end":1170,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1175],"closedAt":1791072015652},{"start":1111,"end":1140,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1145],"closedAt":1791072010652},{"start":1081,"end":1110,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1115],"closedAt":1791072005660},{"start":1051,"end":1080,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1085],"closedAt":1791072000650},{"start":1021,"end":1050,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1055],"closedAt":1791071996151},{"start":991,"end":1020,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1025],"closedAt":1791071991159},{"start":961,"end":990,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[995],"closedAt":1791071985647},{"start":931,"end":960,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[965],"closedAt":1791071980648},{"start":901,"end":930,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[935],"closedAt":1791071975658},{"start":871,"end":900,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[905],"closedAt":1791071970647},{"start":841,"end":870,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[875],"closedAt":1791071966141},{"start":811,"end":840,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[845],"closedAt":1791071961137},{"start":781,"end":810,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[815],"closedAt":1791071955646},{"start":751,"end":780,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[785],"closedAt":1791071950645},{"start":721,"end":750,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[755],"closedAt":1791071945662}],"sentCount":10,"lastSentAt":1791133208329}</v>
+        <v>{"config":{"enabled":true,"channels":[],"siteChannelId":null,"maxR":3,"predictionCount":1,"trigger":"both","blockSize":30,"categoriesOn":{"3/2":false,"3/3":false,"2/2":true},"categoryChannels":{"3/2":[],"3/3":[],"2/2":[-1004387601010]},"categorySiteChannels":{"3/2":null,"3/3":null,"2/2":null}},"history":[{"start":541,"end":570,"counts":{"3/2":2,"3/3":12,"2/2":9},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791192577250},{"start":511,"end":540,"counts":{"3/2":3,"3/3":8,"2/2":14},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791190782081},{"start":481,"end":510,"counts":{"3/2":3,"3/3":10,"2/2":11},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791188947533},{"start":451,"end":480,"counts":{"3/2":4,"3/3":7,"2/2":16},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791187202298},{"start":421,"end":450,"counts":{"3/2":4,"3/3":14,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791185351694},{"start":391,"end":420,"counts":{"3/2":6,"3/3":9,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791183607061},{"start":361,"end":390,"counts":{"3/2":9,"3/3":4,"2/2":14},"predicted":false,"signal":"3/3","selected":false,"targets":[],"closedAt":1791181801954},{"start":331,"end":360,"counts":{"3/2":6,"3/3":7,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791180001818},{"start":301,"end":330,"counts":{"3/2":5,"3/3":14,"2/2":9},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791178206627},{"start":271,"end":300,"counts":{"3/2":6,"3/3":10,"2/2":14},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791176346488},{"start":241,"end":270,"counts":{"3/2":5,"3/3":9,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791174576387},{"start":211,"end":240,"counts":{"3/2":7,"3/3":8,"2/2":12},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791172751174},{"start":181,"end":210,"counts":{"3/2":2,"3/3":16,"2/2":8},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791170976018},{"start":151,"end":180,"counts":{"3/2":7,"3/3":11,"2/2":10},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791169146088},{"start":121,"end":150,"counts":{"3/2":3,"3/3":10,"2/2":15},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791167350792},{"start":91,"end":120,"counts":{"3/2":5,"3/3":11,"2/2":13},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791165550681},{"start":61,"end":90,"counts":{"3/2":5,"3/3":5,"2/2":15},"predicted":false,"signal":null,"selected":false,"targets":[],"closedAt":1791163805538},{"start":31,"end":60,"counts":{"3/2":8,"3/3":11,"2/2":9},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791161976041},{"start":1,"end":30,"counts":{"3/2":5,"3/3":14,"2/2":11},"predicted":false,"signal":"3/2","selected":false,"targets":[],"closedAt":1791160145639},{"start":781,"end":810,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[815],"closedAt":1791158414478},{"start":751,"end":780,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[785],"closedAt":1791158409972},{"start":721,"end":750,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[755],"closedAt":1791158404992},{"start":691,"end":720,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[725],"closedAt":1791158399478},{"start":661,"end":690,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[695],"closedAt":1791158394477},{"start":631,"end":660,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[665],"closedAt":1791158389483},{"start":601,"end":630,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[635],"closedAt":1791158384851},{"start":571,"end":600,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[605],"closedAt":1791158379977},{"start":541,"end":570,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[575],"closedAt":1791158374980},{"start":511,"end":540,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[545],"closedAt":1791158369478},{"start":481,"end":510,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[515],"closedAt":1791158364478},{"start":451,"end":480,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[485],"closedAt":1791158359480},{"start":421,"end":450,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[455],"closedAt":1791158354477},{"start":391,"end":420,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[425],"closedAt":1791158349975},{"start":361,"end":390,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[395],"closedAt":1791158344977},{"start":331,"end":360,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[365],"closedAt":1791158339477},{"start":301,"end":330,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[335],"closedAt":1791158334476},{"start":271,"end":300,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[305],"closedAt":1791158329483},{"start":241,"end":270,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[275],"closedAt":1791158324553},{"start":211,"end":240,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[245],"closedAt":1791158319975},{"start":181,"end":210,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[215],"closedAt":1791158314975},{"start":151,"end":180,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[185],"closedAt":1791158309472},{"start":121,"end":150,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[155],"closedAt":1791158304474},{"start":91,"end":120,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[125],"closedAt":1791158299476},{"start":61,"end":90,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[95],"closedAt":1791158294473},{"start":31,"end":60,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[65],"closedAt":1791158289967},{"start":1,"end":30,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[35],"closedAt":1791158284980},{"start":1381,"end":1410,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1415],"closedAt":1791157739442},{"start":1351,"end":1380,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1385],"closedAt":1791157734444},{"start":1321,"end":1350,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1355],"closedAt":1791157729448},{"start":1291,"end":1320,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1325],"closedAt":1791157724441},{"start":1261,"end":1290,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1295],"closedAt":1791157719935},{"start":1231,"end":1260,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1265],"closedAt":1791157714456},{"start":1201,"end":1230,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1235],"closedAt":1791157709440},{"start":1171,"end":1200,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1205],"closedAt":1791157704440},{"start":1141,"end":1170,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1175],"closedAt":1791157699442},{"start":1111,"end":1140,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1145],"closedAt":1791157694438},{"start":1081,"end":1110,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1115],"closedAt":1791157689934},{"start":1051,"end":1080,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1085],"closedAt":1791157684449},{"start":1021,"end":1050,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1055],"closedAt":1791157679442},{"start":991,"end":1020,"counts":{"3/2":0,"3/3":0,"2/2":0},"predicted":true,"signal":"2/2","selected":true,"targets":[1025],"closedAt":1791157674437}],"sentCount":10,"lastSentAt":1791133208329}</v>
       </c>
     </row>
     <row r="12">
@@ -2498,23 +2615,34 @@
         <v>1</v>
       </c>
       <c r="C13" t="str">
-        <v>{"enabled":true,"channels":[],"maxR":3,"format":5,"strategies":{"costume":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":719,"sentCount":0,"lastSentAt":null,"codeName":"Zéphyr Sablier","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":719},"dominant":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":713,"sentCount":0,"lastSentAt":null,"codeName":"Zéphyr Colibri","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":713},"matchnul":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Zéphyr Colibri","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"parite":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":715,"sentCount":0,"lastSentAt":null,"codeName":"Cyprès Bambou","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":715},"absente":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Fjord Sirocco","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"carteBanquier":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Boréal Sablier","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"ombre":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Vulcan Tornade","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"ombreJoueur":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Cyprès Sirocco","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"dizaine":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Safran Aurore","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"costumeFaible":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Grenat Corail","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"collecte":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Écarlate Tornade","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"predit":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Fjord Panthère","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0}},"history":[],"sentCount":0,"lastSentAt":null}</v>
+        <v>{"enabled":true,"channels":[],"maxR":3,"format":5,"strategies":{"costume":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Zéphyr Sablier","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"dominant":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Zéphyr Colibri","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"matchnul":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Zéphyr Colibri","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"parite":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Cyprès Bambou","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"absente":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Fjord Sirocco","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"carteBanquier":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Boréal Sablier","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"ombre":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Vulcan Tornade","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"ombreJoueur":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Cyprès Sirocco","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"dizaine":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Safran Aurore","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"costumeFaible":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Grenat Corail","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"collecte":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Écarlate Tornade","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0},"predit":{"enabled":false,"channels":[],"counting":false,"needed":0,"seen":0,"armed":false,"pending":null,"lastSeenTarget":0,"sentCount":0,"lastSentAt":null,"codeName":"Fjord Panthère","format":0,"maxR":null,"channelsNote":"","lastTrust":null,"text":"","title":"","autoSend":false,"manualSentCount":0,"lastManualAt":null,"lastNoticeTarget":0}},"history":[],"sentCount":0,"lastSentAt":null}</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>predictionControl</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>{"paused":false,"pausedAt":null,"pauseReason":null,"pausedBy":null,"resumedAt":null,"resumedBy":null,"schedule":null,"lastAutoKey":null,"channels":{"-1004483335797":{"id":"-1004483335797","username":null,"title":"ELI et Kouamé","paused":true,"pausedAt":1791188836703,"reason":null,"by":"canal « ELI et Kouamé »","resumedAt":null,"resumedBy":null,"schedule":null,"lastAutoKey":null}}}</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
         <v>copyAnnounce</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="str">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="str">
         <v>{"config":{"enabled":true},"rules":[],"channelTitles":{},"sentCount":0,"lastSentAt":null}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
